--- a/Financial Analysis/KTOS.xlsx
+++ b/Financial Analysis/KTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B27128-5610-4AF7-831B-49ABDFCD1CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D7D528-85F4-4C8B-9F83-392D3CC0699C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4FA626FF-4A3D-49DE-9837-5D4007C2FA44}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>KTOS</t>
   </si>
@@ -324,16 +324,29 @@
   </si>
   <si>
     <t>Q4 (Dec)</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +406,15 @@
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -640,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -715,6 +737,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1162,14 +1186,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>90.08</v>
+        <v>107.54</v>
       </c>
       <c r="E3" s="5">
-        <v>45930</v>
+        <v>45939</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45930</v>
+        <v>45939</v>
       </c>
       <c r="G3" s="5">
         <v>45960</v>
@@ -1193,7 +1217,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>15205.504000000001</v>
+        <v>18152.752000000004</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1235,7 +1259,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>14591.704000000002</v>
+        <v>17538.952000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1245,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0037CCB-0B59-41FB-A535-43E374CC36C0}">
-  <dimension ref="B2:EG36"/>
+  <dimension ref="B2:EG46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -4746,7 +4770,7 @@
       </c>
       <c r="AI34" s="4">
         <f>Main!D3</f>
-        <v>90.08</v>
+        <v>107.54</v>
       </c>
     </row>
     <row r="35" spans="2:35">
@@ -4863,7 +4887,7 @@
       </c>
       <c r="AI35" s="11">
         <f>AI33/AI34-1</f>
-        <v>-0.87042777033592045</v>
+        <v>-0.89146488331653073</v>
       </c>
     </row>
     <row r="36" spans="2:35">
@@ -4980,6 +5004,50 @@
       </c>
       <c r="AI36" s="7" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35">
+      <c r="B39" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:35">
+      <c r="B40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="2:35">
+      <c r="B41" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" s="34" customFormat="1">
+      <c r="B43" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="J43" s="34">
+        <v>1950.9</v>
+      </c>
+      <c r="L43" s="34">
+        <v>2585.6999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35">
+      <c r="B45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L45" s="35">
+        <f>Main!D9/Model!L43</f>
+        <v>6.7830575859535163</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35">
+      <c r="B46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L46" s="10">
+        <f>L43/Main!D9-1</f>
+        <v>-0.85257385960118948</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/KTOS.xlsx
+++ b/Financial Analysis/KTOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6EA07E-A259-4DA5-9DA2-62EC0E924DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2AEECF-B7D9-40F1-A5CF-C724866CEC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4FA626FF-4A3D-49DE-9837-5D4007C2FA44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FA626FF-4A3D-49DE-9837-5D4007C2FA44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1272,14 +1272,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>82.65</v>
+        <v>69.14</v>
       </c>
       <c r="E3" s="5">
-        <v>45966</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G3" s="5">
         <v>46072</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>13951.320000000002</v>
+        <v>11670.832</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>13385.420000000002</v>
+        <v>11104.932000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AI51" s="4">
         <f>Main!D3</f>
-        <v>82.65</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="52" spans="2:35">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AI52" s="11">
         <f>AI50/AI51-1</f>
-        <v>-0.7601749066060659</v>
+        <v>-0.71331293073461599</v>
       </c>
     </row>
     <row r="53" spans="2:35">
@@ -5655,7 +5655,7 @@
       <c r="L62" s="35"/>
       <c r="V62" s="35">
         <f>Main!$D$9/Model!V60</f>
-        <v>5.5236330623529897</v>
+        <v>4.5825659225023729</v>
       </c>
     </row>
     <row r="63" spans="2:35">
@@ -5665,7 +5665,7 @@
       <c r="L63" s="10"/>
       <c r="V63" s="10">
         <f>V60/Main!$D$9-1</f>
-        <v>-0.81895973379991061</v>
+        <v>-0.78178164440808828</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/KTOS.xlsx
+++ b/Financial Analysis/KTOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2AEECF-B7D9-40F1-A5CF-C724866CEC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A753108-FF2F-4C39-A45D-F9BB86579005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FA626FF-4A3D-49DE-9837-5D4007C2FA44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4FA626FF-4A3D-49DE-9837-5D4007C2FA44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="W24" authorId="0" shapeId="0" xr:uid="{EC71DD73-0C50-4D7C-AED2-E868FC10EC59}">
+    <comment ref="AA24" authorId="0" shapeId="0" xr:uid="{EC71DD73-0C50-4D7C-AED2-E868FC10EC59}">
       <text>
         <r>
           <rPr>
@@ -52,7 +52,32 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-(Q325) we are increasing our full year 2026 organic revenue growth forecast up to 15 percent to 20 percent above our expected increased annual 2025 revenue. Additionally, we are providing a preliminary 2027 organic revenue growth target of 18 percent to 23 percent above this increased 2026 estimated revenue range.</t>
+(Q325) we are increasing our full year 2026 organic revenue growth forecast up to 15 percent to 20 percent above our expected increased annual 2025 revenue. Additionally, we are providing a preliminary 2027 organic revenue growth target of 18 percent to 23 percent above this increased 2026 estimated revenue range.
+(Q425) 1.595-1.675b for FY26</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB24" authorId="0" shapeId="0" xr:uid="{637C303F-91AE-450E-ACF7-2887CCFFC278}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+(Q425) We continue to expect Kratos’ Base Case full year 2027 organic revenue growth to be approximately 18 percent to 23 percent above the full year fiscal 2026 revenue forecast we provided today.</t>
         </r>
       </text>
     </comment>
@@ -61,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
   <si>
     <t>KTOS</t>
   </si>
@@ -400,6 +425,18 @@
   </si>
   <si>
     <t>Total floor space</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -739,7 +776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -825,6 +862,7 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,14 +884,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -870,8 +908,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8542020" y="7620"/>
-          <a:ext cx="0" cy="7414260"/>
+          <a:off x="9326880" y="7620"/>
+          <a:ext cx="0" cy="10523220"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -896,14 +934,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -920,8 +958,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13434060" y="0"/>
-          <a:ext cx="0" cy="7056120"/>
+          <a:off x="16642080" y="0"/>
+          <a:ext cx="0" cy="10530840"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1272,17 +1310,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>69.14</v>
+        <v>91.31</v>
       </c>
       <c r="E3" s="5">
-        <v>45983</v>
+        <v>46078</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45993</v>
+        <v>46078</v>
       </c>
       <c r="G3" s="5">
-        <v>46072</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -1290,11 +1328,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>168.8</f>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -1303,7 +1341,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>11670.832</v>
+        <v>15550.093000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1311,11 +1349,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>565.9</f>
-        <v>565.9</v>
+        <f>560.6+5</f>
+        <v>565.6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -1326,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -1335,7 +1373,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>565.9</v>
+        <v>565.6</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -1344,7 +1382,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>11104.932000000001</v>
+        <v>14984.493</v>
       </c>
     </row>
   </sheetData>
@@ -1354,19 +1392,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0037CCB-0B59-41FB-A535-43E374CC36C0}">
-  <dimension ref="B2:EG63"/>
+  <dimension ref="B2:EK63"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" style="1" customWidth="1"/>
-    <col min="7" max="33" width="8.88671875" style="1"/>
-    <col min="34" max="34" width="13.88671875" style="1" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="37" width="8.88671875" style="1"/>
+    <col min="38" max="38" width="13.88671875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32">
+    <row r="2" spans="2:36">
       <c r="C2" s="7" t="s">
         <v>35</v>
       </c>
@@ -1403,59 +1441,71 @@
       <c r="N2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="1">
+      <c r="O2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" s="1">
         <v>2019</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="U2" s="1">
         <v>2020</v>
       </c>
-      <c r="R2" s="1">
+      <c r="V2" s="1">
         <v>2021</v>
       </c>
-      <c r="S2" s="1">
+      <c r="W2" s="1">
         <v>2022</v>
       </c>
-      <c r="T2" s="1">
+      <c r="X2" s="1">
         <v>2023</v>
       </c>
-      <c r="U2" s="1">
+      <c r="Y2" s="1">
         <v>2024</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Z2" s="1">
         <v>2025</v>
       </c>
-      <c r="W2" s="1">
+      <c r="AA2" s="1">
         <v>2026</v>
       </c>
-      <c r="X2" s="1">
+      <c r="AB2" s="1">
         <v>2027</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2028</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2029</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2030</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2031</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2032</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2033</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2034</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:32">
+    <row r="3" spans="2:36">
       <c r="B3" s="1" t="s">
         <v>109</v>
       </c>
@@ -1471,11 +1521,15 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="U3" s="6">
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="Y3" s="6">
         <v>1600000</v>
       </c>
     </row>
-    <row r="4" spans="2:32">
+    <row r="4" spans="2:36">
       <c r="B4" s="1" t="s">
         <v>110</v>
       </c>
@@ -1491,11 +1545,15 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
-      <c r="U4" s="6">
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="Y4" s="6">
         <v>551000</v>
       </c>
     </row>
-    <row r="5" spans="2:32">
+    <row r="5" spans="2:36">
       <c r="B5" s="1" t="s">
         <v>111</v>
       </c>
@@ -1511,11 +1569,15 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
-      <c r="U5" s="6">
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="Y5" s="6">
         <v>26000</v>
       </c>
     </row>
-    <row r="6" spans="2:32" s="2" customFormat="1">
+    <row r="6" spans="2:36" s="2" customFormat="1">
       <c r="B6" s="2" t="s">
         <v>112</v>
       </c>
@@ -1531,12 +1593,16 @@
       <c r="L6" s="36"/>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
-      <c r="U6" s="9">
-        <f>SUM(U3:U5)</f>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="Y6" s="9">
+        <f>SUM(Y3:Y5)</f>
         <v>2177000</v>
       </c>
     </row>
-    <row r="7" spans="2:32">
+    <row r="7" spans="2:36">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1549,8 +1615,12 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="2:32">
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+    </row>
+    <row r="8" spans="2:36">
       <c r="B8" s="1" t="s">
         <v>108</v>
       </c>
@@ -1581,18 +1651,24 @@
       <c r="M8" s="37">
         <v>1480</v>
       </c>
-      <c r="N8" s="7"/>
-      <c r="T8" s="37">
+      <c r="N8" s="37">
+        <v>1573.4</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="X8" s="37">
         <v>1243.9000000000001</v>
       </c>
-      <c r="U8" s="37">
+      <c r="Y8" s="37">
         <v>1445.1</v>
       </c>
-      <c r="V8" s="37">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="9" spans="2:32">
+      <c r="Z8" s="37">
+        <v>1573.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:36">
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -1605,8 +1681,12 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
-    </row>
-    <row r="10" spans="2:32">
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="2:36">
       <c r="B10" s="1" t="s">
         <v>104</v>
       </c>
@@ -1623,7 +1703,10 @@
       <c r="I10" s="37">
         <v>128.4</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="37">
+        <f>Y10-I10-H10-G10</f>
+        <v>135.30000000000004</v>
+      </c>
       <c r="K10" s="37">
         <v>149.4</v>
       </c>
@@ -1633,18 +1716,28 @@
       <c r="M10" s="37">
         <v>164.7</v>
       </c>
-      <c r="N10" s="7"/>
-      <c r="S10" s="37">
+      <c r="N10" s="37">
+        <f>Z10-M10-L10-K10</f>
+        <v>171.49999999999997</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="W10" s="37">
         <v>420.4</v>
       </c>
-      <c r="T10" s="37">
+      <c r="X10" s="37">
         <v>512.5</v>
       </c>
-      <c r="U10" s="37">
+      <c r="Y10" s="37">
         <v>528</v>
       </c>
-    </row>
-    <row r="11" spans="2:32">
+      <c r="Z10" s="37">
+        <v>672.3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:36">
       <c r="B11" s="1" t="s">
         <v>105</v>
       </c>
@@ -1661,7 +1754,10 @@
       <c r="I11" s="37">
         <v>52.1</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="37">
+        <f t="shared" ref="J11:J12" si="0">Y11-I11-H11-G11</f>
+        <v>51.300000000000011</v>
+      </c>
       <c r="K11" s="37">
         <v>55.3</v>
       </c>
@@ -1671,18 +1767,28 @@
       <c r="M11" s="37">
         <v>55.8</v>
       </c>
-      <c r="N11" s="7"/>
-      <c r="S11" s="37">
+      <c r="N11" s="37">
+        <f t="shared" ref="N11:N12" si="1">Z11-M11-L11-K11</f>
+        <v>65</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="W11" s="37">
         <v>157.5</v>
       </c>
-      <c r="T11" s="37">
+      <c r="X11" s="37">
         <v>192.8</v>
       </c>
-      <c r="U11" s="37">
+      <c r="Y11" s="37">
         <v>195.4</v>
       </c>
-    </row>
-    <row r="12" spans="2:32">
+      <c r="Z11" s="37">
+        <v>228.3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:36">
       <c r="B12" s="1" t="s">
         <v>106</v>
       </c>
@@ -1699,7 +1805,10 @@
       <c r="I12" s="37">
         <v>31.2</v>
       </c>
-      <c r="J12" s="7"/>
+      <c r="J12" s="37">
+        <f t="shared" si="0"/>
+        <v>35.400000000000006</v>
+      </c>
       <c r="K12" s="37">
         <v>34.799999999999997</v>
       </c>
@@ -1709,18 +1818,28 @@
       <c r="M12" s="37">
         <v>39.799999999999997</v>
       </c>
-      <c r="N12" s="7"/>
-      <c r="S12" s="37">
+      <c r="N12" s="37">
+        <f t="shared" si="1"/>
+        <v>40.200000000000003</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="W12" s="37">
         <v>98.7</v>
       </c>
-      <c r="T12" s="37">
+      <c r="X12" s="37">
         <v>119.6</v>
       </c>
-      <c r="U12" s="37">
+      <c r="Y12" s="37">
         <v>142.4</v>
       </c>
-    </row>
-    <row r="13" spans="2:32" s="2" customFormat="1">
+      <c r="Z12" s="37">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:36" s="2" customFormat="1">
       <c r="B13" s="2" t="s">
         <v>103</v>
       </c>
@@ -1740,7 +1859,10 @@
         <f>SUM(I10:I12)</f>
         <v>211.7</v>
       </c>
-      <c r="J13" s="36"/>
+      <c r="J13" s="38">
+        <f>SUM(J10:J12)</f>
+        <v>222.00000000000006</v>
+      </c>
       <c r="K13" s="38">
         <f>SUM(K10:K12)</f>
         <v>239.5</v>
@@ -1753,21 +1875,32 @@
         <f>SUM(M10:M12)</f>
         <v>260.3</v>
       </c>
-      <c r="N13" s="36"/>
-      <c r="S13" s="38">
-        <f>SUM(S10:S12)</f>
+      <c r="N13" s="38">
+        <f>SUM(N10:N12)</f>
+        <v>276.7</v>
+      </c>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="W13" s="38">
+        <f>SUM(W10:W12)</f>
         <v>676.6</v>
       </c>
-      <c r="T13" s="38">
-        <f>SUM(T10:T12)</f>
+      <c r="X13" s="38">
+        <f>SUM(X10:X12)</f>
         <v>824.9</v>
       </c>
-      <c r="U13" s="38">
-        <f>SUM(U10:U12)</f>
+      <c r="Y13" s="38">
+        <f>SUM(Y10:Y12)</f>
         <v>865.8</v>
       </c>
-    </row>
-    <row r="14" spans="2:32">
+      <c r="Z13" s="38">
+        <f>SUM(Z10:Z12)</f>
+        <v>1054.8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:36">
       <c r="B14" s="1" t="s">
         <v>104</v>
       </c>
@@ -1784,7 +1917,10 @@
       <c r="I14" s="37">
         <v>55.5</v>
       </c>
-      <c r="J14" s="7"/>
+      <c r="J14" s="37">
+        <f t="shared" ref="J14:J16" si="2">Y14-I14-H14-G14</f>
+        <v>56.5</v>
+      </c>
       <c r="K14" s="37">
         <v>56.1</v>
       </c>
@@ -1794,18 +1930,28 @@
       <c r="M14" s="37">
         <v>66.400000000000006</v>
       </c>
-      <c r="N14" s="7"/>
-      <c r="S14" s="37">
+      <c r="N14" s="37">
+        <f t="shared" ref="N14:N16" si="3">Z14-M14-L14-K14</f>
+        <v>60.300000000000004</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="W14" s="37">
         <v>203.3</v>
       </c>
-      <c r="T14" s="37">
+      <c r="X14" s="37">
         <v>200.2</v>
       </c>
-      <c r="U14" s="37">
+      <c r="Y14" s="37">
         <v>234</v>
       </c>
-    </row>
-    <row r="15" spans="2:32">
+      <c r="Z14" s="37">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:36">
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
@@ -1822,7 +1968,10 @@
       <c r="I15" s="37">
         <v>6.5</v>
       </c>
-      <c r="J15" s="7"/>
+      <c r="J15" s="37">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
       <c r="K15" s="37">
         <v>5.8</v>
       </c>
@@ -1832,18 +1981,28 @@
       <c r="M15" s="37">
         <v>3.9</v>
       </c>
-      <c r="N15" s="7"/>
-      <c r="S15" s="37">
+      <c r="N15" s="37">
+        <f t="shared" si="3"/>
+        <v>20.599999999999998</v>
+      </c>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="W15" s="37">
         <v>15.6</v>
       </c>
-      <c r="T15" s="37">
+      <c r="X15" s="37">
         <v>9.1999999999999993</v>
       </c>
-      <c r="U15" s="37">
+      <c r="Y15" s="37">
         <v>31.3</v>
       </c>
-    </row>
-    <row r="16" spans="2:32">
+      <c r="Z15" s="37">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36">
       <c r="B16" s="1" t="s">
         <v>106</v>
       </c>
@@ -1860,7 +2019,10 @@
       <c r="I16" s="37">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J16" s="7"/>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000002</v>
+      </c>
       <c r="K16" s="37">
         <v>1.2</v>
       </c>
@@ -1870,18 +2032,28 @@
       <c r="M16" s="37">
         <v>17</v>
       </c>
-      <c r="N16" s="7"/>
-      <c r="S16" s="37">
+      <c r="N16" s="37">
+        <f t="shared" si="3"/>
+        <v>-12.5</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="W16" s="37">
         <v>2.8</v>
       </c>
-      <c r="T16" s="37">
+      <c r="X16" s="37">
         <v>2.8</v>
       </c>
-      <c r="U16" s="37">
+      <c r="Y16" s="37">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="17" spans="2:32" s="2" customFormat="1">
+      <c r="Z16" s="37">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:36" s="2" customFormat="1">
       <c r="B17" s="2" t="s">
         <v>107</v>
       </c>
@@ -1901,7 +2073,10 @@
         <f>SUM(I14:I16)</f>
         <v>64.2</v>
       </c>
-      <c r="J17" s="36"/>
+      <c r="J17" s="38">
+        <f>SUM(J14:J16)</f>
+        <v>61.1</v>
+      </c>
       <c r="K17" s="38">
         <f>SUM(K14:K16)</f>
         <v>63.1</v>
@@ -1914,21 +2089,32 @@
         <f>SUM(M14:M16)</f>
         <v>87.300000000000011</v>
       </c>
-      <c r="N17" s="36"/>
-      <c r="S17" s="38">
-        <f>SUM(S14:S16)</f>
+      <c r="N17" s="38">
+        <f>SUM(N14:N16)</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="W17" s="38">
+        <f>SUM(W14:W16)</f>
         <v>221.70000000000002</v>
       </c>
-      <c r="T17" s="38">
-        <f>SUM(T14:T16)</f>
+      <c r="X17" s="38">
+        <f>SUM(X14:X16)</f>
         <v>212.2</v>
       </c>
-      <c r="U17" s="38">
-        <f>SUM(U14:U16)</f>
+      <c r="Y17" s="38">
+        <f>SUM(Y14:Y16)</f>
         <v>270.5</v>
       </c>
-    </row>
-    <row r="18" spans="2:32" s="2" customFormat="1">
+      <c r="Z17" s="38">
+        <f>SUM(Z14:Z16)</f>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="2:36" s="2" customFormat="1">
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
@@ -1948,7 +2134,10 @@
         <f>SUM(I17,I13)</f>
         <v>275.89999999999998</v>
       </c>
-      <c r="J18" s="36"/>
+      <c r="J18" s="38">
+        <f>SUM(J17,J13)</f>
+        <v>283.10000000000008</v>
+      </c>
       <c r="K18" s="38">
         <f>SUM(K17,K13)</f>
         <v>302.60000000000002</v>
@@ -1961,21 +2150,32 @@
         <f>SUM(M17,M13)</f>
         <v>347.6</v>
       </c>
-      <c r="N18" s="36"/>
-      <c r="S18" s="38">
-        <f>SUM(S17,S13)</f>
+      <c r="N18" s="38">
+        <f>SUM(N17,N13)</f>
+        <v>345.1</v>
+      </c>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="W18" s="38">
+        <f>SUM(W17,W13)</f>
         <v>898.30000000000007</v>
       </c>
-      <c r="T18" s="38">
-        <f>SUM(T17,T13)</f>
+      <c r="X18" s="38">
+        <f>SUM(X17,X13)</f>
         <v>1037.0999999999999</v>
       </c>
-      <c r="U18" s="38">
-        <f>SUM(U17,U13)</f>
+      <c r="Y18" s="38">
+        <f>SUM(Y17,Y13)</f>
         <v>1136.3</v>
       </c>
-    </row>
-    <row r="19" spans="2:32">
+      <c r="Z18" s="38">
+        <f>SUM(Z17,Z13)</f>
+        <v>1346.8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:36">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1988,8 +2188,12 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
-    </row>
-    <row r="20" spans="2:32">
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+    </row>
+    <row r="20" spans="2:36">
       <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
@@ -2005,8 +2209,12 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="2:32">
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+    </row>
+    <row r="21" spans="2:36">
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2019,8 +2227,12 @@
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
-    </row>
-    <row r="22" spans="2:32">
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+    </row>
+    <row r="22" spans="2:36">
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
@@ -2037,7 +2249,7 @@
         <v>103.9</v>
       </c>
       <c r="J22" s="6">
-        <f>U22-I22-H22-G22</f>
+        <f>Y22-I22-H22-G22</f>
         <v>106.5</v>
       </c>
       <c r="K22" s="6">
@@ -2050,73 +2262,76 @@
         <v>117.4</v>
       </c>
       <c r="N22" s="6">
-        <f>J22*1.12</f>
-        <v>119.28000000000002</v>
-      </c>
-      <c r="P22" s="6">
+        <f>Z22-M22-L22-K22</f>
+        <v>114.30000000000001</v>
+      </c>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="T22" s="6">
         <v>272.60000000000002</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="U22" s="6">
         <v>248.7</v>
       </c>
-      <c r="R22" s="6">
+      <c r="V22" s="6">
         <v>219.4</v>
       </c>
-      <c r="S22" s="6">
+      <c r="W22" s="6">
         <v>325.2</v>
       </c>
-      <c r="T22" s="6">
+      <c r="X22" s="6">
         <v>402.6</v>
       </c>
-      <c r="U22" s="6">
+      <c r="Y22" s="6">
         <v>423.4</v>
       </c>
-      <c r="V22" s="6">
-        <f>SUM(K22:N22)</f>
-        <v>473.98000000000008</v>
-      </c>
-      <c r="W22" s="6">
-        <f>V22*1.1</f>
-        <v>521.37800000000016</v>
-      </c>
-      <c r="X22" s="6">
-        <f>W22*1.09</f>
-        <v>568.3020200000002</v>
-      </c>
-      <c r="Y22" s="6">
-        <f>X22*1.06</f>
-        <v>602.40014120000023</v>
-      </c>
       <c r="Z22" s="6">
-        <f>Y22*1.05</f>
-        <v>632.52014826000027</v>
-      </c>
-      <c r="AA22" s="6">
-        <f t="shared" ref="AA22:AF22" si="0">Z22*1.05</f>
-        <v>664.14615567300029</v>
+        <v>469</v>
+      </c>
+      <c r="AA22" s="39">
+        <f>Z22*1.1</f>
+        <v>515.90000000000009</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="0"/>
-        <v>697.35346345665039</v>
+        <f>AA22*1.09</f>
+        <v>562.33100000000013</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="0"/>
-        <v>732.22113662948288</v>
+        <f>AB22*1.07</f>
+        <v>601.69417000000021</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="0"/>
-        <v>768.83219346095711</v>
+        <f>AC22*1.05</f>
+        <v>631.77887850000025</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="0"/>
-        <v>807.27380313400499</v>
+        <f t="shared" ref="AE22:AJ22" si="4">AD22*1.05</f>
+        <v>663.36782242500033</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="0"/>
-        <v>847.63749329070527</v>
-      </c>
-    </row>
-    <row r="23" spans="2:32">
+        <f t="shared" si="4"/>
+        <v>696.53621354625034</v>
+      </c>
+      <c r="AG22" s="6">
+        <f t="shared" si="4"/>
+        <v>731.36302422356289</v>
+      </c>
+      <c r="AH22" s="6">
+        <f t="shared" si="4"/>
+        <v>767.93117543474102</v>
+      </c>
+      <c r="AI22" s="6">
+        <f t="shared" si="4"/>
+        <v>806.32773420647811</v>
+      </c>
+      <c r="AJ22" s="6">
+        <f t="shared" si="4"/>
+        <v>846.64412091680208</v>
+      </c>
+    </row>
+    <row r="23" spans="2:36">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -2133,7 +2348,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="6">
-        <f>U23-I23-H23-G23</f>
+        <f>Y23-I23-H23-G23</f>
         <v>176.59999999999997</v>
       </c>
       <c r="K23" s="6">
@@ -2146,73 +2361,76 @@
         <v>230.2</v>
       </c>
       <c r="N23" s="6">
-        <f>J23*1.17</f>
-        <v>206.62199999999996</v>
-      </c>
-      <c r="P23" s="6">
+        <f t="shared" ref="N23" si="5">Z23-M23-L23-K23</f>
+        <v>230.7999999999999</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="T23" s="6">
         <v>444.9</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="U23" s="6">
         <v>499</v>
       </c>
-      <c r="R23" s="6">
+      <c r="V23" s="6">
         <v>592.1</v>
       </c>
-      <c r="S23" s="6">
+      <c r="W23" s="6">
         <v>573.1</v>
       </c>
-      <c r="T23" s="6">
+      <c r="X23" s="6">
         <v>634.5</v>
       </c>
-      <c r="U23" s="6">
+      <c r="Y23" s="6">
         <v>712.9</v>
       </c>
-      <c r="V23" s="6">
-        <f>SUM(K23:N23)</f>
-        <v>853.62199999999996</v>
-      </c>
-      <c r="W23" s="6">
-        <f>V23*1.25</f>
-        <v>1067.0274999999999</v>
-      </c>
-      <c r="X23" s="6">
-        <f>W23*1.22</f>
-        <v>1301.7735499999999</v>
-      </c>
-      <c r="Y23" s="6">
-        <f>X23*1.14</f>
-        <v>1484.0218469999998</v>
-      </c>
       <c r="Z23" s="6">
-        <f>Y23*1.08</f>
-        <v>1602.74359476</v>
-      </c>
-      <c r="AA23" s="6">
-        <f>Z23*1.06</f>
-        <v>1698.9082104455999</v>
+        <v>877.8</v>
+      </c>
+      <c r="AA23" s="39">
+        <f>Z23*1.25</f>
+        <v>1097.25</v>
       </c>
       <c r="AB23" s="6">
-        <f t="shared" ref="AB23:AF23" si="1">AA23*1.05</f>
-        <v>1783.85362096788</v>
+        <f>AA23*1.22</f>
+        <v>1338.645</v>
       </c>
       <c r="AC23" s="6">
-        <f t="shared" si="1"/>
-        <v>1873.046302016274</v>
+        <f>AB23*1.15</f>
+        <v>1539.44175</v>
       </c>
       <c r="AD23" s="6">
-        <f t="shared" si="1"/>
-        <v>1966.6986171170879</v>
+        <f>AC23*1.08</f>
+        <v>1662.59709</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" si="1"/>
-        <v>2065.0335479729424</v>
+        <f>AD23*1.06</f>
+        <v>1762.3529154</v>
       </c>
       <c r="AF23" s="6">
-        <f t="shared" si="1"/>
-        <v>2168.2852253715896</v>
-      </c>
-    </row>
-    <row r="24" spans="2:32" s="2" customFormat="1">
+        <f t="shared" ref="AF23:AJ23" si="6">AE23*1.05</f>
+        <v>1850.4705611700001</v>
+      </c>
+      <c r="AG23" s="6">
+        <f t="shared" si="6"/>
+        <v>1942.9940892285001</v>
+      </c>
+      <c r="AH23" s="6">
+        <f t="shared" si="6"/>
+        <v>2040.1437936899251</v>
+      </c>
+      <c r="AI23" s="6">
+        <f t="shared" si="6"/>
+        <v>2142.1509833744217</v>
+      </c>
+      <c r="AJ23" s="6">
+        <f t="shared" si="6"/>
+        <v>2249.2585325431428</v>
+      </c>
+    </row>
+    <row r="24" spans="2:36" s="2" customFormat="1">
       <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
@@ -2221,107 +2439,122 @@
         <v>274.60000000000002</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" ref="G24:L24" si="2">G22+G23</f>
+        <f t="shared" ref="G24:L24" si="7">G22+G23</f>
         <v>277.2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>300.10000000000002</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>275.89999999999998</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>283.09999999999997</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>302.60000000000002</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>351.5</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24:N24" si="3">M22+M23</f>
+        <f t="shared" ref="M24:N24" si="8">M22+M23</f>
         <v>347.6</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="3"/>
-        <v>325.90199999999999</v>
+        <f t="shared" si="8"/>
+        <v>345.09999999999991</v>
+      </c>
+      <c r="O24" s="9">
+        <v>340</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24:V24" si="4">P22+P23</f>
+        <f>L24*1.15</f>
+        <v>404.22499999999997</v>
+      </c>
+      <c r="Q24" s="9">
+        <f>M24*1.2</f>
+        <v>417.12</v>
+      </c>
+      <c r="R24" s="9">
+        <f>N24*1.25</f>
+        <v>431.37499999999989</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" ref="T24:Z24" si="9">T22+T23</f>
         <v>717.5</v>
       </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="4"/>
+      <c r="U24" s="9">
+        <f t="shared" si="9"/>
         <v>747.7</v>
       </c>
-      <c r="R24" s="9">
-        <f t="shared" si="4"/>
+      <c r="V24" s="9">
+        <f t="shared" si="9"/>
         <v>811.5</v>
       </c>
-      <c r="S24" s="9">
-        <f t="shared" si="4"/>
+      <c r="W24" s="9">
+        <f t="shared" si="9"/>
         <v>898.3</v>
       </c>
-      <c r="T24" s="9">
-        <f t="shared" si="4"/>
+      <c r="X24" s="9">
+        <f t="shared" si="9"/>
         <v>1037.0999999999999</v>
       </c>
-      <c r="U24" s="9">
-        <f t="shared" si="4"/>
+      <c r="Y24" s="9">
+        <f t="shared" si="9"/>
         <v>1136.3</v>
       </c>
-      <c r="V24" s="9">
-        <f t="shared" si="4"/>
-        <v>1327.6020000000001</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" ref="W24:AF24" si="5">W22+W23</f>
-        <v>1588.4055000000001</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="5"/>
-        <v>1870.07557</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="5"/>
-        <v>2086.4219881999998</v>
-      </c>
       <c r="Z24" s="9">
-        <f t="shared" si="5"/>
-        <v>2235.2637430200002</v>
+        <f t="shared" si="9"/>
+        <v>1346.8</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="5"/>
-        <v>2363.0543661186002</v>
+        <f>SUM(O24:R24)</f>
+        <v>1592.7199999999998</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="5"/>
-        <v>2481.2070844245304</v>
+        <f t="shared" ref="AA24:AJ24" si="10">AB22+AB23</f>
+        <v>1900.9760000000001</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="5"/>
-        <v>2605.267438645757</v>
+        <f t="shared" si="10"/>
+        <v>2141.1359200000002</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="5"/>
-        <v>2735.530810578045</v>
+        <f t="shared" si="10"/>
+        <v>2294.3759685000005</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="5"/>
-        <v>2872.3073511069474</v>
+        <f t="shared" si="10"/>
+        <v>2425.7207378250005</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="5"/>
-        <v>3015.9227186622948</v>
-      </c>
-    </row>
-    <row r="25" spans="2:32">
+        <f t="shared" si="10"/>
+        <v>2547.0067747162502</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="10"/>
+        <v>2674.357113452063</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="10"/>
+        <v>2808.074969124666</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="10"/>
+        <v>2948.4787175808997</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="10"/>
+        <v>3095.9026534599448</v>
+      </c>
+    </row>
+    <row r="25" spans="2:36">
       <c r="B25" s="1" t="s">
         <v>16</v>
       </c>
@@ -2338,7 +2571,7 @@
         <v>76.7</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" ref="J25:J26" si="6">U25-I25-H25-G25</f>
+        <f t="shared" ref="J25:J26" si="11">Y25-I25-H25-G25</f>
         <v>77.100000000000009</v>
       </c>
       <c r="K25" s="6">
@@ -2351,73 +2584,76 @@
         <v>91.2</v>
       </c>
       <c r="N25" s="6">
-        <f>N22*0.75</f>
-        <v>89.460000000000008</v>
-      </c>
-      <c r="P25" s="6">
+        <f t="shared" ref="N25:N26" si="12">Z25-M25-L25-K25</f>
+        <v>82.700000000000031</v>
+      </c>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="T25" s="6">
         <v>192</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="U25" s="6">
         <v>182.5</v>
       </c>
-      <c r="R25" s="6">
+      <c r="V25" s="6">
         <v>156.19999999999999</v>
       </c>
-      <c r="S25" s="6">
+      <c r="W25" s="6">
         <v>239</v>
       </c>
-      <c r="T25" s="6">
+      <c r="X25" s="6">
         <v>303.2</v>
       </c>
-      <c r="U25" s="6">
+      <c r="Y25" s="6">
         <v>310</v>
       </c>
-      <c r="V25" s="6">
-        <f t="shared" ref="V25:V26" si="7">SUM(K25:N25)</f>
-        <v>363.56000000000006</v>
-      </c>
-      <c r="W25" s="6">
-        <f>W22*0.75</f>
-        <v>391.03350000000012</v>
-      </c>
-      <c r="X25" s="6">
-        <f>X22*0.74</f>
-        <v>420.54349480000013</v>
-      </c>
-      <c r="Y25" s="6">
-        <f>Y22*0.73</f>
-        <v>439.75210307600014</v>
-      </c>
       <c r="Z25" s="6">
-        <f>Z22*0.72</f>
-        <v>455.41450674720016</v>
+        <v>356.8</v>
       </c>
       <c r="AA25" s="6">
-        <f>AA22*0.71</f>
-        <v>471.54377052783019</v>
+        <f>AA22*0.75</f>
+        <v>386.92500000000007</v>
       </c>
       <c r="AB25" s="6">
-        <f>AB22*0.7</f>
-        <v>488.14742441965524</v>
+        <f>AB22*0.74</f>
+        <v>416.12494000000009</v>
       </c>
       <c r="AC25" s="6">
-        <f t="shared" ref="AC25:AF25" si="8">AC22*0.7</f>
-        <v>512.55479564063796</v>
+        <f>AC22*0.73</f>
+        <v>439.23674410000012</v>
       </c>
       <c r="AD25" s="6">
-        <f t="shared" si="8"/>
-        <v>538.18253542266996</v>
+        <f>AD22*0.72</f>
+        <v>454.88079252000017</v>
       </c>
       <c r="AE25" s="6">
-        <f t="shared" si="8"/>
-        <v>565.09166219380347</v>
+        <f>AE22*0.71</f>
+        <v>470.9911539217502</v>
       </c>
       <c r="AF25" s="6">
-        <f t="shared" si="8"/>
-        <v>593.34624530349367</v>
-      </c>
-    </row>
-    <row r="26" spans="2:32">
+        <f>AF22*0.7</f>
+        <v>487.5753494823752</v>
+      </c>
+      <c r="AG25" s="6">
+        <f t="shared" ref="AG25:AJ25" si="13">AG22*0.7</f>
+        <v>511.95411695649398</v>
+      </c>
+      <c r="AH25" s="6">
+        <f t="shared" si="13"/>
+        <v>537.5518228043187</v>
+      </c>
+      <c r="AI25" s="6">
+        <f t="shared" si="13"/>
+        <v>564.42941394453464</v>
+      </c>
+      <c r="AJ25" s="6">
+        <f t="shared" si="13"/>
+        <v>592.65088464176142</v>
+      </c>
+    </row>
+    <row r="26" spans="2:36">
       <c r="B26" s="1" t="s">
         <v>17</v>
       </c>
@@ -2434,7 +2670,7 @@
         <v>130</v>
       </c>
       <c r="J26" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>136.20000000000005</v>
       </c>
       <c r="K26" s="6">
@@ -2447,73 +2683,76 @@
         <v>179.3</v>
       </c>
       <c r="N26" s="6">
-        <f>N23*0.77</f>
-        <v>159.09893999999997</v>
-      </c>
-      <c r="P26" s="6">
+        <f t="shared" si="12"/>
+        <v>179</v>
+      </c>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="T26" s="6">
         <v>335.5</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="U26" s="6">
         <v>362</v>
       </c>
-      <c r="R26" s="6">
+      <c r="V26" s="6">
         <v>430.2</v>
       </c>
-      <c r="S26" s="6">
+      <c r="W26" s="6">
         <v>433.3</v>
       </c>
-      <c r="T26" s="6">
+      <c r="X26" s="6">
         <v>465.3</v>
       </c>
-      <c r="U26" s="6">
+      <c r="Y26" s="6">
         <v>539.1</v>
       </c>
-      <c r="V26" s="6">
-        <f t="shared" si="7"/>
-        <v>662.19893999999999</v>
-      </c>
-      <c r="W26" s="6">
-        <f>W23*0.76</f>
-        <v>810.94089999999994</v>
-      </c>
-      <c r="X26" s="6">
-        <f>X23*0.75</f>
-        <v>976.33016249999991</v>
-      </c>
-      <c r="Y26" s="6">
-        <f t="shared" ref="Y26:AF26" si="9">Y23*0.75</f>
-        <v>1113.0163852499998</v>
-      </c>
       <c r="Z26" s="6">
-        <f t="shared" si="9"/>
-        <v>1202.05769607</v>
+        <v>682.1</v>
       </c>
       <c r="AA26" s="6">
-        <f t="shared" si="9"/>
-        <v>1274.1811578341999</v>
+        <f>AA23*0.76</f>
+        <v>833.91</v>
       </c>
       <c r="AB26" s="6">
-        <f t="shared" si="9"/>
-        <v>1337.8902157259099</v>
+        <f>AB23*0.75</f>
+        <v>1003.98375</v>
       </c>
       <c r="AC26" s="6">
-        <f t="shared" si="9"/>
-        <v>1404.7847265122055</v>
+        <f>AC23*0.74</f>
+        <v>1139.186895</v>
       </c>
       <c r="AD26" s="6">
-        <f t="shared" si="9"/>
-        <v>1475.0239628378158</v>
+        <f>AD23*0.73</f>
+        <v>1213.6958757</v>
       </c>
       <c r="AE26" s="6">
-        <f t="shared" si="9"/>
-        <v>1548.7751609797069</v>
+        <f t="shared" ref="AE26:AJ26" si="14">AE23*0.73</f>
+        <v>1286.517628242</v>
       </c>
       <c r="AF26" s="6">
-        <f t="shared" si="9"/>
-        <v>1626.2139190286921</v>
-      </c>
-    </row>
-    <row r="27" spans="2:32">
+        <f t="shared" si="14"/>
+        <v>1350.8435096541</v>
+      </c>
+      <c r="AG26" s="6">
+        <f t="shared" si="14"/>
+        <v>1418.385685136805</v>
+      </c>
+      <c r="AH26" s="6">
+        <f t="shared" si="14"/>
+        <v>1489.3049693936453</v>
+      </c>
+      <c r="AI26" s="6">
+        <f t="shared" si="14"/>
+        <v>1563.7702178633278</v>
+      </c>
+      <c r="AJ26" s="6">
+        <f t="shared" si="14"/>
+        <v>1641.9587287564941</v>
+      </c>
+    </row>
+    <row r="27" spans="2:36">
       <c r="B27" s="1" t="s">
         <v>18</v>
       </c>
@@ -2522,107 +2761,111 @@
         <v>201.2</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" ref="G27:L27" si="10">G25+G26</f>
+        <f t="shared" ref="G27:L27" si="15">G25+G26</f>
         <v>206.2</v>
       </c>
       <c r="H27" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>222.9</v>
       </c>
       <c r="I27" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>206.7</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>213.30000000000007</v>
       </c>
       <c r="K27" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>229</v>
       </c>
       <c r="L27" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>277.7</v>
       </c>
       <c r="M27" s="6">
-        <f t="shared" ref="M27:N27" si="11">M25+M26</f>
+        <f t="shared" ref="M27:N27" si="16">M25+M26</f>
         <v>270.5</v>
       </c>
       <c r="N27" s="6">
-        <f t="shared" si="11"/>
-        <v>248.55893999999998</v>
-      </c>
-      <c r="P27" s="6">
-        <f t="shared" ref="P27:W27" si="12">P25+P26</f>
+        <f t="shared" si="16"/>
+        <v>261.70000000000005</v>
+      </c>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="T27" s="6">
+        <f t="shared" ref="T27:AA27" si="17">T25+T26</f>
         <v>527.5</v>
       </c>
-      <c r="Q27" s="6">
-        <f t="shared" si="12"/>
+      <c r="U27" s="6">
+        <f t="shared" si="17"/>
         <v>544.5</v>
       </c>
-      <c r="R27" s="6">
-        <f t="shared" si="12"/>
+      <c r="V27" s="6">
+        <f t="shared" si="17"/>
         <v>586.4</v>
       </c>
-      <c r="S27" s="6">
-        <f t="shared" si="12"/>
+      <c r="W27" s="6">
+        <f t="shared" si="17"/>
         <v>672.3</v>
       </c>
-      <c r="T27" s="6">
-        <f t="shared" si="12"/>
+      <c r="X27" s="6">
+        <f t="shared" si="17"/>
         <v>768.5</v>
       </c>
-      <c r="U27" s="6">
-        <f t="shared" si="12"/>
+      <c r="Y27" s="6">
+        <f t="shared" si="17"/>
         <v>849.1</v>
       </c>
-      <c r="V27" s="6">
-        <f t="shared" si="12"/>
-        <v>1025.7589400000002</v>
-      </c>
-      <c r="W27" s="6">
-        <f t="shared" si="12"/>
-        <v>1201.9744000000001</v>
-      </c>
-      <c r="X27" s="6">
-        <f t="shared" ref="X27:AF27" si="13">X25+X26</f>
-        <v>1396.8736573000001</v>
-      </c>
-      <c r="Y27" s="6">
-        <f t="shared" si="13"/>
-        <v>1552.7684883259999</v>
-      </c>
       <c r="Z27" s="6">
-        <f t="shared" si="13"/>
-        <v>1657.4722028172002</v>
+        <f t="shared" si="17"/>
+        <v>1038.9000000000001</v>
       </c>
       <c r="AA27" s="6">
-        <f t="shared" si="13"/>
-        <v>1745.7249283620301</v>
+        <f t="shared" si="17"/>
+        <v>1220.835</v>
       </c>
       <c r="AB27" s="6">
-        <f t="shared" si="13"/>
-        <v>1826.0376401455651</v>
+        <f t="shared" ref="AB27:AJ27" si="18">AB25+AB26</f>
+        <v>1420.10869</v>
       </c>
       <c r="AC27" s="6">
-        <f t="shared" si="13"/>
-        <v>1917.3395221528435</v>
+        <f t="shared" si="18"/>
+        <v>1578.4236391000002</v>
       </c>
       <c r="AD27" s="6">
-        <f t="shared" si="13"/>
-        <v>2013.2064982604857</v>
+        <f t="shared" si="18"/>
+        <v>1668.5766682200001</v>
       </c>
       <c r="AE27" s="6">
-        <f t="shared" si="13"/>
-        <v>2113.8668231735105</v>
+        <f t="shared" si="18"/>
+        <v>1757.5087821637503</v>
       </c>
       <c r="AF27" s="6">
-        <f t="shared" si="13"/>
-        <v>2219.5601643321856</v>
-      </c>
-    </row>
-    <row r="28" spans="2:32" s="2" customFormat="1">
+        <f t="shared" si="18"/>
+        <v>1838.4188591364752</v>
+      </c>
+      <c r="AG27" s="6">
+        <f t="shared" si="18"/>
+        <v>1930.3398020932991</v>
+      </c>
+      <c r="AH27" s="6">
+        <f t="shared" si="18"/>
+        <v>2026.8567921979638</v>
+      </c>
+      <c r="AI27" s="6">
+        <f t="shared" si="18"/>
+        <v>2128.1996318078627</v>
+      </c>
+      <c r="AJ27" s="6">
+        <f t="shared" si="18"/>
+        <v>2234.6096133982555</v>
+      </c>
+    </row>
+    <row r="28" spans="2:36" s="2" customFormat="1">
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
@@ -2631,107 +2874,111 @@
         <v>73.400000000000034</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:L28" si="14">G24-G27</f>
+        <f t="shared" ref="G28:L28" si="19">G24-G27</f>
         <v>71</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>77.200000000000017</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>69.199999999999989</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>69.799999999999898</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>73.600000000000023</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>73.800000000000011</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28:N28" si="15">M24-M27</f>
+        <f t="shared" ref="M28:N28" si="20">M24-M27</f>
         <v>77.100000000000023</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="15"/>
-        <v>77.343060000000008</v>
-      </c>
-      <c r="P28" s="9">
-        <f t="shared" ref="P28:W28" si="16">P24-P27</f>
+        <f t="shared" si="20"/>
+        <v>83.399999999999864</v>
+      </c>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="T28" s="9">
+        <f t="shared" ref="T28:AA28" si="21">T24-T27</f>
         <v>190</v>
       </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="16"/>
+      <c r="U28" s="9">
+        <f t="shared" si="21"/>
         <v>203.20000000000005</v>
       </c>
-      <c r="R28" s="9">
-        <f t="shared" si="16"/>
+      <c r="V28" s="9">
+        <f t="shared" si="21"/>
         <v>225.10000000000002</v>
       </c>
-      <c r="S28" s="9">
-        <f t="shared" si="16"/>
+      <c r="W28" s="9">
+        <f t="shared" si="21"/>
         <v>226</v>
       </c>
-      <c r="T28" s="9">
-        <f t="shared" si="16"/>
+      <c r="X28" s="9">
+        <f t="shared" si="21"/>
         <v>268.59999999999991</v>
       </c>
-      <c r="U28" s="9">
-        <f t="shared" si="16"/>
+      <c r="Y28" s="9">
+        <f t="shared" si="21"/>
         <v>287.19999999999993</v>
       </c>
-      <c r="V28" s="9">
-        <f t="shared" si="16"/>
-        <v>301.84305999999992</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="16"/>
-        <v>386.43110000000001</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" ref="X28:AF28" si="17">X24-X27</f>
-        <v>473.20191269999987</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="17"/>
-        <v>533.65349987399986</v>
-      </c>
       <c r="Z28" s="9">
-        <f t="shared" si="17"/>
-        <v>577.79154020279998</v>
+        <f t="shared" si="21"/>
+        <v>307.89999999999986</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="17"/>
-        <v>617.32943775657009</v>
+        <f t="shared" si="21"/>
+        <v>371.88499999999976</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="17"/>
-        <v>655.16944427896533</v>
+        <f t="shared" ref="AB28:AJ28" si="22">AB24-AB27</f>
+        <v>480.86731000000009</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="17"/>
-        <v>687.92791649291348</v>
+        <f t="shared" si="22"/>
+        <v>562.7122809</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="17"/>
-        <v>722.32431231755936</v>
+        <f t="shared" si="22"/>
+        <v>625.79930028000035</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="17"/>
-        <v>758.4405279334369</v>
+        <f t="shared" si="22"/>
+        <v>668.21195566125016</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="17"/>
-        <v>796.36255433010911</v>
-      </c>
-    </row>
-    <row r="29" spans="2:32">
+        <f t="shared" si="22"/>
+        <v>708.58791557977497</v>
+      </c>
+      <c r="AG28" s="9">
+        <f t="shared" si="22"/>
+        <v>744.01731135876389</v>
+      </c>
+      <c r="AH28" s="9">
+        <f t="shared" si="22"/>
+        <v>781.2181769267022</v>
+      </c>
+      <c r="AI28" s="9">
+        <f t="shared" si="22"/>
+        <v>820.27908577303697</v>
+      </c>
+      <c r="AJ28" s="9">
+        <f t="shared" si="22"/>
+        <v>861.29304006168923</v>
+      </c>
+    </row>
+    <row r="29" spans="2:36">
       <c r="B29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2748,7 +2995,7 @@
         <v>52.6</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" ref="J29:J32" si="18">U29-I29-H29-G29</f>
+        <f t="shared" ref="J29:J32" si="23">Y29-I29-H29-G29</f>
         <v>52.500000000000007</v>
       </c>
       <c r="K29" s="6">
@@ -2761,73 +3008,76 @@
         <v>59.8</v>
       </c>
       <c r="N29" s="6">
-        <f>J29*1.08</f>
-        <v>56.70000000000001</v>
-      </c>
-      <c r="P29" s="6">
+        <f t="shared" ref="N29:N31" si="24">Z29-M29-L29-K29</f>
+        <v>63.499999999999972</v>
+      </c>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="T29" s="6">
         <v>130.80000000000001</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="U29" s="6">
         <v>144.5</v>
       </c>
-      <c r="R29" s="6">
+      <c r="V29" s="6">
         <v>160.19999999999999</v>
       </c>
-      <c r="S29" s="6">
+      <c r="W29" s="6">
         <v>182.8</v>
       </c>
-      <c r="T29" s="6">
+      <c r="X29" s="6">
         <v>197.8</v>
       </c>
-      <c r="U29" s="6">
+      <c r="Y29" s="6">
         <v>214</v>
       </c>
-      <c r="V29" s="6">
-        <f t="shared" ref="V29:V32" si="19">SUM(K29:N29)</f>
-        <v>233.4</v>
-      </c>
-      <c r="W29" s="6">
-        <f>V29*1.04</f>
-        <v>242.73600000000002</v>
-      </c>
-      <c r="X29" s="6">
-        <f>W29*1.03</f>
-        <v>250.01808000000003</v>
-      </c>
-      <c r="Y29" s="6">
-        <f>X29*1.02</f>
-        <v>255.01844160000002</v>
-      </c>
       <c r="Z29" s="6">
-        <f>Y29*1.02</f>
-        <v>260.11881043200003</v>
+        <v>240.2</v>
       </c>
       <c r="AA29" s="6">
-        <f>Z29*1.01</f>
-        <v>262.71999853632002</v>
+        <f>Z29*1.04</f>
+        <v>249.80799999999999</v>
       </c>
       <c r="AB29" s="6">
-        <f t="shared" ref="AB29:AF29" si="20">AA29*1.01</f>
-        <v>265.3471985216832</v>
+        <f>AA29*1.03</f>
+        <v>257.30223999999998</v>
       </c>
       <c r="AC29" s="6">
-        <f t="shared" si="20"/>
-        <v>268.00067050690001</v>
+        <f>AB29*1.02</f>
+        <v>262.44828480000001</v>
       </c>
       <c r="AD29" s="6">
-        <f t="shared" si="20"/>
-        <v>270.680677211969</v>
+        <f>AC29*1.02</f>
+        <v>267.69725049600004</v>
       </c>
       <c r="AE29" s="6">
-        <f t="shared" si="20"/>
-        <v>273.3874839840887</v>
+        <f>AD29*1.01</f>
+        <v>270.37422300096006</v>
       </c>
       <c r="AF29" s="6">
-        <f t="shared" si="20"/>
-        <v>276.1213588239296</v>
-      </c>
-    </row>
-    <row r="30" spans="2:32">
+        <f t="shared" ref="AF29:AJ29" si="25">AE29*1.01</f>
+        <v>273.07796523096965</v>
+      </c>
+      <c r="AG29" s="6">
+        <f t="shared" si="25"/>
+        <v>275.80874488327936</v>
+      </c>
+      <c r="AH29" s="6">
+        <f t="shared" si="25"/>
+        <v>278.56683233211214</v>
+      </c>
+      <c r="AI29" s="6">
+        <f t="shared" si="25"/>
+        <v>281.35250065543329</v>
+      </c>
+      <c r="AJ29" s="6">
+        <f t="shared" si="25"/>
+        <v>284.16602566198765</v>
+      </c>
+    </row>
+    <row r="30" spans="2:36">
       <c r="B30" s="1" t="s">
         <v>41</v>
       </c>
@@ -2840,7 +3090,7 @@
         <v>0.2</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="K30" s="6"/>
@@ -2849,41 +3099,33 @@
         <v>0.2</v>
       </c>
       <c r="N30" s="6">
-        <v>0</v>
-      </c>
-      <c r="P30" s="6">
+        <f t="shared" si="24"/>
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="T30" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q30" s="6">
+      <c r="U30" s="6">
         <v>1.7</v>
       </c>
-      <c r="R30" s="6">
+      <c r="V30" s="6">
         <v>1.8</v>
       </c>
-      <c r="S30" s="6">
+      <c r="W30" s="6">
         <v>0.7</v>
       </c>
-      <c r="T30" s="6">
+      <c r="X30" s="6">
         <v>0.4</v>
       </c>
-      <c r="U30" s="6">
+      <c r="Y30" s="6">
         <v>0.7</v>
       </c>
-      <c r="V30" s="6">
-        <f t="shared" si="19"/>
-        <v>0.2</v>
-      </c>
-      <c r="W30" s="6">
-        <v>0</v>
-      </c>
-      <c r="X30" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="6">
-        <v>0</v>
-      </c>
       <c r="Z30" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" s="6">
         <v>0</v>
@@ -2903,8 +3145,20 @@
       <c r="AF30" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:32">
+      <c r="AG30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:36">
       <c r="B31" s="1" t="s">
         <v>20</v>
       </c>
@@ -2921,7 +3175,7 @@
         <v>9.9</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>10.6</v>
       </c>
       <c r="K31" s="6">
@@ -2934,72 +3188,84 @@
         <v>10</v>
       </c>
       <c r="N31" s="6">
-        <v>11</v>
+        <f t="shared" si="24"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O31" s="6">
+        <v>11.5</v>
       </c>
       <c r="P31" s="6">
+        <v>11.7</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="R31" s="6">
+        <v>12</v>
+      </c>
+      <c r="T31" s="6">
         <v>18</v>
       </c>
-      <c r="Q31" s="6">
+      <c r="U31" s="6">
         <v>27</v>
       </c>
-      <c r="R31" s="6">
+      <c r="V31" s="6">
         <v>35.200000000000003</v>
       </c>
-      <c r="S31" s="6">
+      <c r="W31" s="6">
         <v>38.6</v>
       </c>
-      <c r="T31" s="6">
+      <c r="X31" s="6">
         <v>38.4</v>
       </c>
-      <c r="U31" s="6">
+      <c r="Y31" s="6">
         <v>40.299999999999997</v>
       </c>
-      <c r="V31" s="6">
-        <f t="shared" si="19"/>
-        <v>41.2</v>
-      </c>
-      <c r="W31" s="6">
-        <f>V31*1.02</f>
-        <v>42.024000000000001</v>
-      </c>
-      <c r="X31" s="6">
-        <f t="shared" ref="X31:AF31" si="21">W31*1.02</f>
-        <v>42.86448</v>
-      </c>
-      <c r="Y31" s="6">
-        <f t="shared" si="21"/>
-        <v>43.721769600000002</v>
-      </c>
       <c r="Z31" s="6">
-        <f t="shared" si="21"/>
-        <v>44.596204992000004</v>
+        <v>40</v>
       </c>
       <c r="AA31" s="6">
-        <f t="shared" si="21"/>
-        <v>45.488129091840008</v>
+        <f>Z31*1.15</f>
+        <v>46</v>
       </c>
       <c r="AB31" s="6">
-        <f t="shared" si="21"/>
-        <v>46.39789167367681</v>
+        <f>AA31*1.08</f>
+        <v>49.680000000000007</v>
       </c>
       <c r="AC31" s="6">
-        <f t="shared" si="21"/>
-        <v>47.325849507150345</v>
+        <f>AB31*1.05</f>
+        <v>52.164000000000009</v>
       </c>
       <c r="AD31" s="6">
-        <f t="shared" si="21"/>
-        <v>48.272366497293355</v>
+        <f>AC31*1.03</f>
+        <v>53.728920000000009</v>
       </c>
       <c r="AE31" s="6">
-        <f t="shared" si="21"/>
-        <v>49.237813827239222</v>
+        <f t="shared" ref="AB31:AJ31" si="26">AD31*1.02</f>
+        <v>54.803498400000009</v>
       </c>
       <c r="AF31" s="6">
-        <f t="shared" si="21"/>
-        <v>50.222570103784008</v>
-      </c>
-    </row>
-    <row r="32" spans="2:32">
+        <f t="shared" si="26"/>
+        <v>55.899568368000011</v>
+      </c>
+      <c r="AG31" s="6">
+        <f t="shared" si="26"/>
+        <v>57.01755973536001</v>
+      </c>
+      <c r="AH31" s="6">
+        <f t="shared" si="26"/>
+        <v>58.15791093006721</v>
+      </c>
+      <c r="AI31" s="6">
+        <f t="shared" si="26"/>
+        <v>59.321069148668556</v>
+      </c>
+      <c r="AJ31" s="6">
+        <f t="shared" si="26"/>
+        <v>60.507490531641928</v>
+      </c>
+    </row>
+    <row r="32" spans="2:36">
       <c r="B32" s="1" t="s">
         <v>40</v>
       </c>
@@ -3012,49 +3278,37 @@
         <v>0</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>3.2</v>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
-      <c r="M32" s="6">
-        <v>0</v>
-      </c>
-      <c r="N32" s="6">
-        <v>0</v>
-      </c>
-      <c r="P32" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="R32" s="6">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6">
-        <v>6.8</v>
-      </c>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
       <c r="T32" s="6">
         <v>0.9</v>
       </c>
       <c r="U32" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="V32" s="6">
+        <v>0</v>
+      </c>
+      <c r="W32" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="X32" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="Y32" s="6">
         <v>3.2</v>
       </c>
-      <c r="V32" s="6">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="6">
-        <v>0</v>
-      </c>
-      <c r="X32" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="6">
-        <v>0</v>
-      </c>
       <c r="Z32" s="6">
+        <f t="shared" ref="Z29:Z32" si="27">SUM(K32:N32)</f>
         <v>0</v>
       </c>
       <c r="AA32" s="6">
@@ -3075,8 +3329,20 @@
       <c r="AF32" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:137">
+      <c r="AG32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:141">
       <c r="B33" s="1" t="s">
         <v>39</v>
       </c>
@@ -3101,91 +3367,95 @@
         <v>66.800000000000011</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" ref="K33:L33" si="22">SUM(K29:K31)</f>
+        <f t="shared" ref="K33:L33" si="28">SUM(K29:K31)</f>
         <v>67</v>
       </c>
       <c r="L33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>70.099999999999994</v>
       </c>
       <c r="M33" s="6">
-        <f t="shared" ref="M33" si="23">SUM(M29:M31)</f>
+        <f t="shared" ref="M33" si="29">SUM(M29:M31)</f>
         <v>70</v>
       </c>
       <c r="N33" s="6">
-        <f t="shared" ref="N33" si="24">SUM(N29:N31)</f>
-        <v>67.700000000000017</v>
-      </c>
-      <c r="P33" s="6">
-        <f t="shared" ref="P33:W33" si="25">SUM(P29:P32)</f>
+        <f t="shared" ref="N33" si="30">SUM(N29:N31)</f>
+        <v>75.199999999999974</v>
+      </c>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="T33" s="6">
+        <f t="shared" ref="T33:AA33" si="31">SUM(T29:T32)</f>
         <v>152.00000000000003</v>
       </c>
-      <c r="Q33" s="6">
-        <f t="shared" si="25"/>
+      <c r="U33" s="6">
+        <f t="shared" si="31"/>
         <v>173.89999999999998</v>
       </c>
-      <c r="R33" s="6">
-        <f t="shared" si="25"/>
+      <c r="V33" s="6">
+        <f t="shared" si="31"/>
         <v>197.2</v>
       </c>
-      <c r="S33" s="6">
-        <f t="shared" si="25"/>
+      <c r="W33" s="6">
+        <f t="shared" si="31"/>
         <v>228.9</v>
       </c>
-      <c r="T33" s="6">
-        <f t="shared" si="25"/>
+      <c r="X33" s="6">
+        <f t="shared" si="31"/>
         <v>237.50000000000003</v>
       </c>
-      <c r="U33" s="6">
-        <f t="shared" si="25"/>
+      <c r="Y33" s="6">
+        <f t="shared" si="31"/>
         <v>258.2</v>
       </c>
-      <c r="V33" s="6">
-        <f t="shared" si="25"/>
-        <v>274.8</v>
-      </c>
-      <c r="W33" s="6">
-        <f t="shared" si="25"/>
-        <v>284.76</v>
-      </c>
-      <c r="X33" s="6">
-        <f t="shared" ref="X33:AF33" si="26">SUM(X29:X32)</f>
-        <v>292.88256000000001</v>
-      </c>
-      <c r="Y33" s="6">
-        <f t="shared" si="26"/>
-        <v>298.74021120000003</v>
-      </c>
       <c r="Z33" s="6">
-        <f t="shared" si="26"/>
-        <v>304.71501542400006</v>
+        <f t="shared" si="31"/>
+        <v>282.29999999999995</v>
       </c>
       <c r="AA33" s="6">
-        <f t="shared" si="26"/>
-        <v>308.20812762816001</v>
+        <f t="shared" si="31"/>
+        <v>295.80799999999999</v>
       </c>
       <c r="AB33" s="6">
-        <f t="shared" si="26"/>
-        <v>311.74509019536004</v>
+        <f t="shared" ref="AB33:AJ33" si="32">SUM(AB29:AB32)</f>
+        <v>306.98223999999999</v>
       </c>
       <c r="AC33" s="6">
-        <f t="shared" si="26"/>
-        <v>315.32652001405035</v>
+        <f t="shared" si="32"/>
+        <v>314.6122848</v>
       </c>
       <c r="AD33" s="6">
-        <f t="shared" si="26"/>
-        <v>318.95304370926237</v>
+        <f t="shared" si="32"/>
+        <v>321.42617049600005</v>
       </c>
       <c r="AE33" s="6">
-        <f t="shared" si="26"/>
-        <v>322.62529781132793</v>
+        <f t="shared" si="32"/>
+        <v>325.17772140096008</v>
       </c>
       <c r="AF33" s="6">
-        <f t="shared" si="26"/>
-        <v>326.34392892771359</v>
-      </c>
-    </row>
-    <row r="34" spans="2:137" s="2" customFormat="1">
+        <f t="shared" si="32"/>
+        <v>328.97753359896967</v>
+      </c>
+      <c r="AG33" s="6">
+        <f t="shared" si="32"/>
+        <v>332.82630461863937</v>
+      </c>
+      <c r="AH33" s="6">
+        <f t="shared" si="32"/>
+        <v>336.72474326217935</v>
+      </c>
+      <c r="AI33" s="6">
+        <f t="shared" si="32"/>
+        <v>340.67356980410182</v>
+      </c>
+      <c r="AJ33" s="6">
+        <f t="shared" si="32"/>
+        <v>344.67351619362955</v>
+      </c>
+    </row>
+    <row r="34" spans="2:141" s="2" customFormat="1">
       <c r="B34" s="2" t="s">
         <v>21</v>
       </c>
@@ -3194,11 +3464,11 @@
         <v>12.200000000000031</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:H34" si="27">G28-G33</f>
+        <f t="shared" ref="G34:H34" si="33">G28-G33</f>
         <v>7</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>12.500000000000014</v>
       </c>
       <c r="I34" s="9">
@@ -3210,7 +3480,7 @@
         <v>2.9999999999998863</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" ref="K34" si="28">K28-K33</f>
+        <f t="shared" ref="K34" si="34">K28-K33</f>
         <v>6.6000000000000227</v>
       </c>
       <c r="L34" s="9">
@@ -3218,83 +3488,89 @@
         <v>3.7000000000000171</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" ref="M34:N34" si="29">M28-M33</f>
+        <f t="shared" ref="M34:N34" si="35">M28-M33</f>
         <v>7.1000000000000227</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="29"/>
-        <v>9.6430599999999913</v>
-      </c>
-      <c r="P34" s="9">
-        <f t="shared" ref="P34:W34" si="30">P28-P33</f>
+        <f t="shared" si="35"/>
+        <v>8.1999999999998892</v>
+      </c>
+      <c r="O34" s="9">
+        <v>3</v>
+      </c>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="T34" s="9">
+        <f t="shared" ref="T34:AA34" si="36">T28-T33</f>
         <v>37.999999999999972</v>
       </c>
-      <c r="Q34" s="9">
-        <f t="shared" si="30"/>
+      <c r="U34" s="9">
+        <f t="shared" si="36"/>
         <v>29.300000000000068</v>
       </c>
-      <c r="R34" s="9">
-        <f t="shared" si="30"/>
+      <c r="V34" s="9">
+        <f t="shared" si="36"/>
         <v>27.900000000000034</v>
       </c>
-      <c r="S34" s="9">
-        <f t="shared" si="30"/>
+      <c r="W34" s="9">
+        <f t="shared" si="36"/>
         <v>-2.9000000000000057</v>
       </c>
-      <c r="T34" s="9">
-        <f t="shared" si="30"/>
+      <c r="X34" s="9">
+        <f t="shared" si="36"/>
         <v>31.099999999999881</v>
       </c>
-      <c r="U34" s="9">
-        <f t="shared" si="30"/>
+      <c r="Y34" s="9">
+        <f t="shared" si="36"/>
         <v>28.999999999999943</v>
       </c>
-      <c r="V34" s="9">
-        <f t="shared" si="30"/>
-        <v>27.043059999999912</v>
-      </c>
-      <c r="W34" s="9">
-        <f t="shared" si="30"/>
-        <v>101.67110000000002</v>
-      </c>
-      <c r="X34" s="9">
-        <f t="shared" ref="X34:AF34" si="31">X28-X33</f>
-        <v>180.31935269999985</v>
-      </c>
-      <c r="Y34" s="9">
-        <f t="shared" si="31"/>
-        <v>234.91328867399983</v>
-      </c>
       <c r="Z34" s="9">
-        <f t="shared" si="31"/>
-        <v>273.07652477879992</v>
+        <f t="shared" si="36"/>
+        <v>25.599999999999909</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" si="31"/>
-        <v>309.12131012841007</v>
+        <f t="shared" si="36"/>
+        <v>76.076999999999771</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="31"/>
-        <v>343.42435408360529</v>
+        <f t="shared" ref="AB34:AJ34" si="37">AB28-AB33</f>
+        <v>173.8850700000001</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="31"/>
-        <v>372.60139647886314</v>
+        <f t="shared" si="37"/>
+        <v>248.0999961</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="31"/>
-        <v>403.37126860829699</v>
+        <f t="shared" si="37"/>
+        <v>304.3731297840003</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="31"/>
-        <v>435.81523012210897</v>
+        <f t="shared" si="37"/>
+        <v>343.03423426029008</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="31"/>
-        <v>470.01862540239551</v>
-      </c>
-    </row>
-    <row r="35" spans="2:137">
+        <f t="shared" si="37"/>
+        <v>379.6103819808053</v>
+      </c>
+      <c r="AG34" s="9">
+        <f t="shared" si="37"/>
+        <v>411.19100674012452</v>
+      </c>
+      <c r="AH34" s="9">
+        <f t="shared" si="37"/>
+        <v>444.49343366452285</v>
+      </c>
+      <c r="AI34" s="9">
+        <f t="shared" si="37"/>
+        <v>479.60551596893515</v>
+      </c>
+      <c r="AJ34" s="9">
+        <f t="shared" si="37"/>
+        <v>516.61952386805967</v>
+      </c>
+    </row>
+    <row r="35" spans="2:141">
       <c r="B35" s="1" t="s">
         <v>22</v>
       </c>
@@ -3311,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="6">
-        <f t="shared" ref="J35:J36" si="32">U35-I35-H35-G35</f>
+        <f t="shared" ref="J35:J36" si="38">Y35-I35-H35-G35</f>
         <v>0.30000000000000027</v>
       </c>
       <c r="K35" s="6">
@@ -3324,72 +3600,76 @@
         <v>-0.2</v>
       </c>
       <c r="N35" s="6">
-        <v>1</v>
-      </c>
-      <c r="P35" s="6">
+        <f t="shared" ref="N35:N36" si="39">Z35-M35-L35-K35</f>
+        <v>-7.8000000000000007</v>
+      </c>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="T35" s="6">
         <v>21.6</v>
       </c>
-      <c r="Q35" s="6">
+      <c r="U35" s="6">
         <v>22.8</v>
       </c>
-      <c r="R35" s="6">
+      <c r="V35" s="6">
         <v>23.4</v>
       </c>
-      <c r="S35" s="6">
+      <c r="W35" s="6">
         <v>17.7</v>
       </c>
-      <c r="T35" s="6">
+      <c r="X35" s="6">
         <v>20.5</v>
       </c>
-      <c r="U35" s="6">
+      <c r="Y35" s="6">
         <v>3</v>
       </c>
-      <c r="V35" s="6">
-        <f t="shared" ref="V35:V36" si="33">SUM(K35:N35)</f>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="W35" s="6">
-        <f>V35*1.03</f>
-        <v>2.9870000000000005</v>
-      </c>
-      <c r="X35" s="6">
-        <f t="shared" ref="X35:AF35" si="34">W35*1.03</f>
-        <v>3.0766100000000005</v>
-      </c>
-      <c r="Y35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.1689083000000005</v>
-      </c>
       <c r="Z35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.2639755490000004</v>
+        <v>-5.9</v>
       </c>
       <c r="AA35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.3618948154700004</v>
+        <f>Z35*1.03</f>
+        <v>-6.0770000000000008</v>
       </c>
       <c r="AB35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.4627516599341006</v>
+        <f t="shared" ref="AB35:AJ35" si="40">AA35*1.03</f>
+        <v>-6.259310000000001</v>
       </c>
       <c r="AC35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.5666342097321238</v>
+        <f t="shared" si="40"/>
+        <v>-6.4470893000000009</v>
       </c>
       <c r="AD35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.6736332360240875</v>
+        <f t="shared" si="40"/>
+        <v>-6.6405019790000015</v>
       </c>
       <c r="AE35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.78384223310481</v>
+        <f t="shared" si="40"/>
+        <v>-6.8397170383700017</v>
       </c>
       <c r="AF35" s="6">
-        <f t="shared" si="34"/>
-        <v>3.8973575000979546</v>
-      </c>
-    </row>
-    <row r="36" spans="2:137">
+        <f t="shared" si="40"/>
+        <v>-7.0449085495211019</v>
+      </c>
+      <c r="AG35" s="6">
+        <f t="shared" si="40"/>
+        <v>-7.2562558060067355</v>
+      </c>
+      <c r="AH35" s="6">
+        <f t="shared" si="40"/>
+        <v>-7.4739434801869375</v>
+      </c>
+      <c r="AI35" s="6">
+        <f t="shared" si="40"/>
+        <v>-7.6981617845925463</v>
+      </c>
+      <c r="AJ35" s="6">
+        <f t="shared" si="40"/>
+        <v>-7.9291066381303228</v>
+      </c>
+    </row>
+    <row r="36" spans="2:141">
       <c r="B36" s="1" t="s">
         <v>23</v>
       </c>
@@ -3406,7 +3686,7 @@
         <v>0.7</v>
       </c>
       <c r="J36" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>-1.2999999999999998</v>
       </c>
       <c r="K36" s="6">
@@ -3419,42 +3699,34 @@
         <v>-4.8</v>
       </c>
       <c r="N36" s="6">
-        <v>0</v>
-      </c>
-      <c r="P36" s="6">
+        <f t="shared" si="39"/>
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="T36" s="6">
         <v>0.7</v>
       </c>
-      <c r="Q36" s="6">
+      <c r="U36" s="6">
         <v>-0.3</v>
       </c>
-      <c r="R36" s="6">
+      <c r="V36" s="6">
         <v>0.1</v>
       </c>
-      <c r="S36" s="6">
+      <c r="W36" s="6">
         <f>13-0.6</f>
         <v>12.4</v>
       </c>
-      <c r="T36" s="6">
+      <c r="X36" s="6">
         <v>-0.5</v>
       </c>
-      <c r="U36" s="6">
+      <c r="Y36" s="6">
         <v>-0.5</v>
       </c>
-      <c r="V36" s="6">
-        <f t="shared" si="33"/>
-        <v>-6.6</v>
-      </c>
-      <c r="W36" s="6">
-        <v>0</v>
-      </c>
-      <c r="X36" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="6">
-        <v>0</v>
-      </c>
       <c r="Z36" s="6">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AA36" s="6">
         <v>0</v>
@@ -3474,8 +3746,20 @@
       <c r="AF36" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:137" s="2" customFormat="1">
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:141" s="2" customFormat="1">
       <c r="B37" s="2" t="s">
         <v>24</v>
       </c>
@@ -3484,107 +3768,111 @@
         <v>6.8000000000000318</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" ref="G37:L37" si="35">G34-G35-G36</f>
+        <f t="shared" ref="G37:L37" si="41">G34-G35-G36</f>
         <v>4</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>12.700000000000014</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>5.7999999999999856</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>3.9999999999998859</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>5.4000000000000226</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>4.6000000000000174</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" ref="M37:N37" si="36">M34-M35-M36</f>
+        <f t="shared" ref="M37:N37" si="42">M34-M35-M36</f>
         <v>12.100000000000023</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="36"/>
-        <v>8.6430599999999913</v>
-      </c>
-      <c r="P37" s="9">
-        <f t="shared" ref="P37:W37" si="37">P34-P35-P36</f>
+        <f t="shared" si="42"/>
+        <v>11.899999999999888</v>
+      </c>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="T37" s="9">
+        <f t="shared" ref="T37:AA37" si="43">T34-T35-T36</f>
         <v>15.699999999999971</v>
       </c>
-      <c r="Q37" s="9">
-        <f t="shared" si="37"/>
+      <c r="U37" s="9">
+        <f t="shared" si="43"/>
         <v>6.8000000000000673</v>
       </c>
-      <c r="R37" s="9">
-        <f t="shared" si="37"/>
+      <c r="V37" s="9">
+        <f t="shared" si="43"/>
         <v>4.4000000000000359</v>
       </c>
-      <c r="S37" s="9">
-        <f t="shared" si="37"/>
+      <c r="W37" s="9">
+        <f t="shared" si="43"/>
         <v>-33.000000000000007</v>
       </c>
-      <c r="T37" s="9">
-        <f t="shared" si="37"/>
+      <c r="X37" s="9">
+        <f t="shared" si="43"/>
         <v>11.099999999999881</v>
       </c>
-      <c r="U37" s="9">
-        <f t="shared" si="37"/>
+      <c r="Y37" s="9">
+        <f t="shared" si="43"/>
         <v>26.499999999999943</v>
       </c>
-      <c r="V37" s="9">
-        <f t="shared" si="37"/>
-        <v>30.743059999999915</v>
-      </c>
-      <c r="W37" s="9">
-        <f t="shared" si="37"/>
-        <v>98.684100000000029</v>
-      </c>
-      <c r="X37" s="9">
-        <f t="shared" ref="X37:AF37" si="38">X34-X35-X36</f>
-        <v>177.24274269999987</v>
-      </c>
-      <c r="Y37" s="9">
-        <f t="shared" si="38"/>
-        <v>231.74438037399983</v>
-      </c>
       <c r="Z37" s="9">
-        <f t="shared" si="38"/>
-        <v>269.81254922979991</v>
+        <f t="shared" si="43"/>
+        <v>33.999999999999908</v>
       </c>
       <c r="AA37" s="9">
-        <f t="shared" si="38"/>
-        <v>305.75941531294006</v>
+        <f t="shared" si="43"/>
+        <v>82.153999999999769</v>
       </c>
       <c r="AB37" s="9">
-        <f t="shared" si="38"/>
-        <v>339.9616024236712</v>
+        <f t="shared" ref="AB37:AJ37" si="44">AB34-AB35-AB36</f>
+        <v>180.1443800000001</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="38"/>
-        <v>369.03476226913102</v>
+        <f t="shared" si="44"/>
+        <v>254.54708539999999</v>
       </c>
       <c r="AD37" s="9">
-        <f t="shared" si="38"/>
-        <v>399.69763537227288</v>
+        <f t="shared" si="44"/>
+        <v>311.01363176300032</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="38"/>
-        <v>432.03138788900418</v>
+        <f t="shared" si="44"/>
+        <v>349.87395129866007</v>
       </c>
       <c r="AF37" s="9">
-        <f t="shared" si="38"/>
-        <v>466.12126790229757</v>
-      </c>
-    </row>
-    <row r="38" spans="2:137">
+        <f t="shared" si="44"/>
+        <v>386.6552905303264</v>
+      </c>
+      <c r="AG37" s="9">
+        <f t="shared" si="44"/>
+        <v>418.44726254613124</v>
+      </c>
+      <c r="AH37" s="9">
+        <f t="shared" si="44"/>
+        <v>451.96737714470981</v>
+      </c>
+      <c r="AI37" s="9">
+        <f t="shared" si="44"/>
+        <v>487.30367775352772</v>
+      </c>
+      <c r="AJ37" s="9">
+        <f t="shared" si="44"/>
+        <v>524.54863050618997</v>
+      </c>
+    </row>
+    <row r="38" spans="2:141">
       <c r="B38" s="1" t="s">
         <v>25</v>
       </c>
@@ -3601,7 +3889,7 @@
         <v>2.6</v>
       </c>
       <c r="J38" s="6">
-        <f>U38-I38-H38-G38</f>
+        <f>Y38-I38-H38-G38</f>
         <v>9.9999999999999645E-2</v>
       </c>
       <c r="K38" s="6">
@@ -3614,73 +3902,76 @@
         <v>3.2</v>
       </c>
       <c r="N38" s="6">
-        <f>N37*0.2</f>
-        <v>1.7286119999999983</v>
-      </c>
-      <c r="P38" s="6">
+        <f>Z38-M38-L38-K38</f>
+        <v>6.2</v>
+      </c>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="T38" s="6">
         <v>4.8</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="U38" s="6">
         <v>-73.5</v>
       </c>
-      <c r="R38" s="6">
+      <c r="V38" s="6">
         <v>3.9</v>
       </c>
-      <c r="S38" s="6">
+      <c r="W38" s="6">
         <v>0.2</v>
       </c>
-      <c r="T38" s="6">
+      <c r="X38" s="6">
         <v>8.6999999999999993</v>
       </c>
-      <c r="U38" s="6">
+      <c r="Y38" s="6">
         <v>10.199999999999999</v>
       </c>
-      <c r="V38" s="6">
-        <f>SUM(K38:N38)</f>
-        <v>7.528611999999999</v>
-      </c>
-      <c r="W38" s="6">
-        <f>W37*0.2</f>
-        <v>19.736820000000009</v>
-      </c>
-      <c r="X38" s="6">
-        <f t="shared" ref="X38:AF38" si="39">X37*0.2</f>
-        <v>35.448548539999976</v>
-      </c>
-      <c r="Y38" s="6">
-        <f t="shared" si="39"/>
-        <v>46.348876074799968</v>
-      </c>
       <c r="Z38" s="6">
-        <f t="shared" si="39"/>
-        <v>53.962509845959985</v>
+        <v>12</v>
       </c>
       <c r="AA38" s="6">
-        <f t="shared" si="39"/>
-        <v>61.151883062588013</v>
+        <f>AA37*0.2</f>
+        <v>16.430799999999955</v>
       </c>
       <c r="AB38" s="6">
-        <f t="shared" si="39"/>
-        <v>67.992320484734236</v>
+        <f t="shared" ref="AB38:AJ38" si="45">AB37*0.2</f>
+        <v>36.028876000000018</v>
       </c>
       <c r="AC38" s="6">
-        <f t="shared" si="39"/>
-        <v>73.806952453826213</v>
+        <f t="shared" si="45"/>
+        <v>50.909417079999997</v>
       </c>
       <c r="AD38" s="6">
-        <f t="shared" si="39"/>
-        <v>79.939527074454588</v>
+        <f t="shared" si="45"/>
+        <v>62.202726352600067</v>
       </c>
       <c r="AE38" s="6">
-        <f t="shared" si="39"/>
-        <v>86.406277577800836</v>
+        <f t="shared" si="45"/>
+        <v>69.974790259732018</v>
       </c>
       <c r="AF38" s="6">
-        <f t="shared" si="39"/>
-        <v>93.224253580459518</v>
-      </c>
-    </row>
-    <row r="39" spans="2:137" s="2" customFormat="1">
+        <f t="shared" si="45"/>
+        <v>77.331058106065285</v>
+      </c>
+      <c r="AG38" s="6">
+        <f t="shared" si="45"/>
+        <v>83.689452509226257</v>
+      </c>
+      <c r="AH38" s="6">
+        <f t="shared" si="45"/>
+        <v>90.393475428941969</v>
+      </c>
+      <c r="AI38" s="6">
+        <f t="shared" si="45"/>
+        <v>97.46073555070555</v>
+      </c>
+      <c r="AJ38" s="6">
+        <f t="shared" si="45"/>
+        <v>104.90972610123799</v>
+      </c>
+    </row>
+    <row r="39" spans="2:141" s="2" customFormat="1">
       <c r="B39" s="2" t="s">
         <v>26</v>
       </c>
@@ -3689,527 +3980,531 @@
         <v>3.000000000000032</v>
       </c>
       <c r="G39" s="9">
-        <f t="shared" ref="G39:L39" si="40">G37-G38</f>
+        <f t="shared" ref="G39:L39" si="46">G37-G38</f>
         <v>1.2999999999999998</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>7.9000000000000137</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>3.1999999999999855</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>3.8999999999998862</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>4.5000000000000222</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.9000000000000172</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" ref="M39:N39" si="41">M37-M38</f>
+        <f t="shared" ref="M39:N39" si="47">M37-M38</f>
         <v>8.9000000000000234</v>
       </c>
       <c r="N39" s="9">
-        <f t="shared" si="41"/>
-        <v>6.914447999999993</v>
-      </c>
-      <c r="P39" s="9">
-        <f t="shared" ref="P39:W39" si="42">P37-P38</f>
+        <f t="shared" si="47"/>
+        <v>5.6999999999998883</v>
+      </c>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="T39" s="9">
+        <f t="shared" ref="T39:AA39" si="48">T37-T38</f>
         <v>10.89999999999997</v>
       </c>
-      <c r="Q39" s="9">
-        <f t="shared" si="42"/>
+      <c r="U39" s="9">
+        <f t="shared" si="48"/>
         <v>80.300000000000068</v>
       </c>
-      <c r="R39" s="9">
-        <f t="shared" si="42"/>
+      <c r="V39" s="9">
+        <f t="shared" si="48"/>
         <v>0.50000000000003597</v>
       </c>
-      <c r="S39" s="9">
-        <f t="shared" si="42"/>
+      <c r="W39" s="9">
+        <f t="shared" si="48"/>
         <v>-33.20000000000001</v>
       </c>
-      <c r="T39" s="9">
-        <f t="shared" si="42"/>
+      <c r="X39" s="9">
+        <f t="shared" si="48"/>
         <v>2.3999999999998813</v>
       </c>
-      <c r="U39" s="9">
-        <f t="shared" si="42"/>
+      <c r="Y39" s="9">
+        <f t="shared" si="48"/>
         <v>16.299999999999944</v>
       </c>
-      <c r="V39" s="9">
-        <f t="shared" si="42"/>
-        <v>23.214447999999916</v>
-      </c>
-      <c r="W39" s="9">
-        <f t="shared" si="42"/>
-        <v>78.947280000000021</v>
-      </c>
-      <c r="X39" s="9">
-        <f t="shared" ref="X39:AF39" si="43">X37-X38</f>
-        <v>141.7941941599999</v>
-      </c>
-      <c r="Y39" s="9">
-        <f t="shared" si="43"/>
-        <v>185.39550429919987</v>
-      </c>
       <c r="Z39" s="9">
-        <f t="shared" si="43"/>
-        <v>215.85003938383994</v>
+        <f t="shared" si="48"/>
+        <v>21.999999999999908</v>
       </c>
       <c r="AA39" s="9">
-        <f t="shared" si="43"/>
-        <v>244.60753225035205</v>
+        <f t="shared" si="48"/>
+        <v>65.723199999999821</v>
       </c>
       <c r="AB39" s="9">
-        <f t="shared" si="43"/>
-        <v>271.96928193893694</v>
+        <f t="shared" ref="AB39:AJ39" si="49">AB37-AB38</f>
+        <v>144.11550400000007</v>
       </c>
       <c r="AC39" s="9">
-        <f t="shared" si="43"/>
-        <v>295.22780981530479</v>
+        <f t="shared" si="49"/>
+        <v>203.63766831999999</v>
       </c>
       <c r="AD39" s="9">
-        <f t="shared" si="43"/>
-        <v>319.7581082978183</v>
+        <f t="shared" si="49"/>
+        <v>248.81090541040027</v>
       </c>
       <c r="AE39" s="9">
-        <f t="shared" si="43"/>
-        <v>345.62511031120334</v>
+        <f t="shared" si="49"/>
+        <v>279.89916103892807</v>
       </c>
       <c r="AF39" s="9">
-        <f t="shared" si="43"/>
-        <v>372.89701432183807</v>
-      </c>
-      <c r="AG39" s="2">
-        <f>AF39*(1+$AI$45)</f>
-        <v>369.16804417861971</v>
-      </c>
-      <c r="AH39" s="2">
-        <f t="shared" ref="AH39:CS39" si="44">AG39*(1+$AI$45)</f>
-        <v>365.47636373683349</v>
-      </c>
-      <c r="AI39" s="2">
-        <f t="shared" si="44"/>
-        <v>361.82160009946517</v>
-      </c>
-      <c r="AJ39" s="2">
-        <f t="shared" si="44"/>
-        <v>358.20338409847051</v>
+        <f t="shared" si="49"/>
+        <v>309.32423242426114</v>
+      </c>
+      <c r="AG39" s="9">
+        <f t="shared" si="49"/>
+        <v>334.75781003690497</v>
+      </c>
+      <c r="AH39" s="9">
+        <f t="shared" si="49"/>
+        <v>361.57390171576787</v>
+      </c>
+      <c r="AI39" s="9">
+        <f t="shared" si="49"/>
+        <v>389.8429422028222</v>
+      </c>
+      <c r="AJ39" s="9">
+        <f t="shared" si="49"/>
+        <v>419.63890440495197</v>
       </c>
       <c r="AK39" s="2">
-        <f t="shared" si="44"/>
-        <v>354.6213502574858</v>
+        <f>AJ39*(1+$AM$45)</f>
+        <v>415.44251536090246</v>
       </c>
       <c r="AL39" s="2">
-        <f t="shared" si="44"/>
-        <v>351.07513675491094</v>
+        <f t="shared" ref="AL39:CW39" si="50">AK39*(1+$AM$45)</f>
+        <v>411.28809020729341</v>
       </c>
       <c r="AM39" s="2">
-        <f t="shared" si="44"/>
-        <v>347.56438538736182</v>
+        <f t="shared" si="50"/>
+        <v>407.17520930522045</v>
       </c>
       <c r="AN39" s="2">
-        <f t="shared" si="44"/>
-        <v>344.08874153348819</v>
+        <f t="shared" si="50"/>
+        <v>403.10345721216822</v>
       </c>
       <c r="AO39" s="2">
-        <f t="shared" si="44"/>
-        <v>340.6478541181533</v>
+        <f t="shared" si="50"/>
+        <v>399.07242264004651</v>
       </c>
       <c r="AP39" s="2">
-        <f t="shared" si="44"/>
-        <v>337.24137557697179</v>
+        <f t="shared" si="50"/>
+        <v>395.08169841364605</v>
       </c>
       <c r="AQ39" s="2">
-        <f t="shared" si="44"/>
-        <v>333.86896182120205</v>
+        <f t="shared" si="50"/>
+        <v>391.1308814295096</v>
       </c>
       <c r="AR39" s="2">
-        <f t="shared" si="44"/>
-        <v>330.53027220299003</v>
+        <f t="shared" si="50"/>
+        <v>387.21957261521447</v>
       </c>
       <c r="AS39" s="2">
-        <f t="shared" si="44"/>
-        <v>327.22496948096011</v>
+        <f t="shared" si="50"/>
+        <v>383.34737688906233</v>
       </c>
       <c r="AT39" s="2">
-        <f t="shared" si="44"/>
-        <v>323.95271978615051</v>
+        <f t="shared" si="50"/>
+        <v>379.51390312017173</v>
       </c>
       <c r="AU39" s="2">
-        <f t="shared" si="44"/>
-        <v>320.71319258828902</v>
+        <f t="shared" si="50"/>
+        <v>375.71876408897003</v>
       </c>
       <c r="AV39" s="2">
-        <f t="shared" si="44"/>
-        <v>317.50606066240613</v>
+        <f t="shared" si="50"/>
+        <v>371.96157644808034</v>
       </c>
       <c r="AW39" s="2">
-        <f t="shared" si="44"/>
-        <v>314.33100005578206</v>
+        <f t="shared" si="50"/>
+        <v>368.24196068359953</v>
       </c>
       <c r="AX39" s="2">
-        <f t="shared" si="44"/>
-        <v>311.18769005522421</v>
+        <f t="shared" si="50"/>
+        <v>364.55954107676354</v>
       </c>
       <c r="AY39" s="2">
-        <f t="shared" si="44"/>
-        <v>308.07581315467195</v>
+        <f t="shared" si="50"/>
+        <v>360.91394566599593</v>
       </c>
       <c r="AZ39" s="2">
-        <f t="shared" si="44"/>
-        <v>304.99505502312525</v>
+        <f t="shared" si="50"/>
+        <v>357.30480620933594</v>
       </c>
       <c r="BA39" s="2">
-        <f t="shared" si="44"/>
-        <v>301.945104472894</v>
+        <f t="shared" si="50"/>
+        <v>353.7317581472426</v>
       </c>
       <c r="BB39" s="2">
-        <f t="shared" si="44"/>
-        <v>298.92565342816505</v>
+        <f t="shared" si="50"/>
+        <v>350.19444056577015</v>
       </c>
       <c r="BC39" s="2">
-        <f t="shared" si="44"/>
-        <v>295.9363968938834</v>
+        <f t="shared" si="50"/>
+        <v>346.69249616011246</v>
       </c>
       <c r="BD39" s="2">
-        <f t="shared" si="44"/>
-        <v>292.97703292494458</v>
+        <f t="shared" si="50"/>
+        <v>343.22557119851132</v>
       </c>
       <c r="BE39" s="2">
-        <f t="shared" si="44"/>
-        <v>290.04726259569514</v>
+        <f t="shared" si="50"/>
+        <v>339.79331548652618</v>
       </c>
       <c r="BF39" s="2">
-        <f t="shared" si="44"/>
-        <v>287.14678996973817</v>
+        <f t="shared" si="50"/>
+        <v>336.39538233166093</v>
       </c>
       <c r="BG39" s="2">
-        <f t="shared" si="44"/>
-        <v>284.27532207004077</v>
+        <f t="shared" si="50"/>
+        <v>333.03142850834433</v>
       </c>
       <c r="BH39" s="2">
-        <f t="shared" si="44"/>
-        <v>281.43256884934038</v>
+        <f t="shared" si="50"/>
+        <v>329.7011142232609</v>
       </c>
       <c r="BI39" s="2">
-        <f t="shared" si="44"/>
-        <v>278.61824316084699</v>
+        <f t="shared" si="50"/>
+        <v>326.40410308102827</v>
       </c>
       <c r="BJ39" s="2">
-        <f t="shared" si="44"/>
-        <v>275.83206072923849</v>
+        <f t="shared" si="50"/>
+        <v>323.14006205021798</v>
       </c>
       <c r="BK39" s="2">
-        <f t="shared" si="44"/>
-        <v>273.07374012194612</v>
+        <f t="shared" si="50"/>
+        <v>319.90866142971578</v>
       </c>
       <c r="BL39" s="2">
-        <f t="shared" si="44"/>
-        <v>270.34300272072664</v>
+        <f t="shared" si="50"/>
+        <v>316.70957481541859</v>
       </c>
       <c r="BM39" s="2">
-        <f t="shared" si="44"/>
-        <v>267.63957269351937</v>
+        <f t="shared" si="50"/>
+        <v>313.54247906726442</v>
       </c>
       <c r="BN39" s="2">
-        <f t="shared" si="44"/>
-        <v>264.96317696658417</v>
+        <f t="shared" si="50"/>
+        <v>310.40705427659179</v>
       </c>
       <c r="BO39" s="2">
-        <f t="shared" si="44"/>
-        <v>262.31354519691831</v>
+        <f t="shared" si="50"/>
+        <v>307.3029837338259</v>
       </c>
       <c r="BP39" s="2">
-        <f t="shared" si="44"/>
-        <v>259.69040974494914</v>
+        <f t="shared" si="50"/>
+        <v>304.22995389648764</v>
       </c>
       <c r="BQ39" s="2">
-        <f t="shared" si="44"/>
-        <v>257.09350564749963</v>
+        <f t="shared" si="50"/>
+        <v>301.18765435752277</v>
       </c>
       <c r="BR39" s="2">
-        <f t="shared" si="44"/>
-        <v>254.52257059102462</v>
+        <f t="shared" si="50"/>
+        <v>298.17577781394755</v>
       </c>
       <c r="BS39" s="2">
-        <f t="shared" si="44"/>
-        <v>251.97734488511438</v>
+        <f t="shared" si="50"/>
+        <v>295.19402003580808</v>
       </c>
       <c r="BT39" s="2">
-        <f t="shared" si="44"/>
-        <v>249.45757143626324</v>
+        <f t="shared" si="50"/>
+        <v>292.24207983545</v>
       </c>
       <c r="BU39" s="2">
-        <f t="shared" si="44"/>
-        <v>246.9629957219006</v>
+        <f t="shared" si="50"/>
+        <v>289.31965903709551</v>
       </c>
       <c r="BV39" s="2">
-        <f t="shared" si="44"/>
-        <v>244.49336576468158</v>
+        <f t="shared" si="50"/>
+        <v>286.42646244672454</v>
       </c>
       <c r="BW39" s="2">
-        <f t="shared" si="44"/>
-        <v>242.04843210703476</v>
+        <f t="shared" si="50"/>
+        <v>283.5621978222573</v>
       </c>
       <c r="BX39" s="2">
-        <f t="shared" si="44"/>
-        <v>239.62794778596441</v>
+        <f t="shared" si="50"/>
+        <v>280.72657584403476</v>
       </c>
       <c r="BY39" s="2">
-        <f t="shared" si="44"/>
-        <v>237.23166830810476</v>
+        <f t="shared" si="50"/>
+        <v>277.91931008559442</v>
       </c>
       <c r="BZ39" s="2">
-        <f t="shared" si="44"/>
-        <v>234.85935162502372</v>
+        <f t="shared" si="50"/>
+        <v>275.14011698473848</v>
       </c>
       <c r="CA39" s="2">
-        <f t="shared" si="44"/>
-        <v>232.51075810877347</v>
+        <f t="shared" si="50"/>
+        <v>272.3887158148911</v>
       </c>
       <c r="CB39" s="2">
-        <f t="shared" si="44"/>
-        <v>230.18565052768574</v>
+        <f t="shared" si="50"/>
+        <v>269.6648286567422</v>
       </c>
       <c r="CC39" s="2">
-        <f t="shared" si="44"/>
-        <v>227.88379402240886</v>
+        <f t="shared" si="50"/>
+        <v>266.96818037017476</v>
       </c>
       <c r="CD39" s="2">
-        <f t="shared" si="44"/>
-        <v>225.60495608218477</v>
+        <f t="shared" si="50"/>
+        <v>264.29849856647303</v>
       </c>
       <c r="CE39" s="2">
-        <f t="shared" si="44"/>
-        <v>223.34890652136292</v>
+        <f t="shared" si="50"/>
+        <v>261.6555135808083</v>
       </c>
       <c r="CF39" s="2">
-        <f t="shared" si="44"/>
-        <v>221.11541745614929</v>
+        <f t="shared" si="50"/>
+        <v>259.03895844500022</v>
       </c>
       <c r="CG39" s="2">
-        <f t="shared" si="44"/>
-        <v>218.90426328158779</v>
+        <f t="shared" si="50"/>
+        <v>256.44856886055021</v>
       </c>
       <c r="CH39" s="2">
-        <f t="shared" si="44"/>
-        <v>216.71522064877192</v>
+        <f t="shared" si="50"/>
+        <v>253.8840831719447</v>
       </c>
       <c r="CI39" s="2">
-        <f t="shared" si="44"/>
-        <v>214.5480684422842</v>
+        <f t="shared" si="50"/>
+        <v>251.34524234022524</v>
       </c>
       <c r="CJ39" s="2">
-        <f t="shared" si="44"/>
-        <v>212.40258775786137</v>
+        <f t="shared" si="50"/>
+        <v>248.831789916823</v>
       </c>
       <c r="CK39" s="2">
-        <f t="shared" si="44"/>
-        <v>210.27856188028275</v>
+        <f t="shared" si="50"/>
+        <v>246.34347201765476</v>
       </c>
       <c r="CL39" s="2">
-        <f t="shared" si="44"/>
-        <v>208.17577626147991</v>
+        <f t="shared" si="50"/>
+        <v>243.88003729747822</v>
       </c>
       <c r="CM39" s="2">
-        <f t="shared" si="44"/>
-        <v>206.0940184988651</v>
+        <f t="shared" si="50"/>
+        <v>241.44123692450344</v>
       </c>
       <c r="CN39" s="2">
-        <f t="shared" si="44"/>
-        <v>204.03307831387644</v>
+        <f t="shared" si="50"/>
+        <v>239.0268245552584</v>
       </c>
       <c r="CO39" s="2">
-        <f t="shared" si="44"/>
-        <v>201.99274753073769</v>
+        <f t="shared" si="50"/>
+        <v>236.63655630970581</v>
       </c>
       <c r="CP39" s="2">
-        <f t="shared" si="44"/>
-        <v>199.9728200554303</v>
+        <f t="shared" si="50"/>
+        <v>234.27019074660876</v>
       </c>
       <c r="CQ39" s="2">
-        <f t="shared" si="44"/>
-        <v>197.973091854876</v>
+        <f t="shared" si="50"/>
+        <v>231.92748883914268</v>
       </c>
       <c r="CR39" s="2">
-        <f t="shared" si="44"/>
-        <v>195.99336093632724</v>
+        <f t="shared" si="50"/>
+        <v>229.60821395075126</v>
       </c>
       <c r="CS39" s="2">
-        <f t="shared" si="44"/>
-        <v>194.03342732696396</v>
+        <f t="shared" si="50"/>
+        <v>227.31213181124375</v>
       </c>
       <c r="CT39" s="2">
-        <f t="shared" ref="CT39:EG39" si="45">CS39*(1+$AI$45)</f>
-        <v>192.09309305369433</v>
+        <f t="shared" si="50"/>
+        <v>225.03901049313131</v>
       </c>
       <c r="CU39" s="2">
-        <f t="shared" si="45"/>
-        <v>190.17216212315739</v>
+        <f t="shared" si="50"/>
+        <v>222.7886203882</v>
       </c>
       <c r="CV39" s="2">
-        <f t="shared" si="45"/>
-        <v>188.2704405019258</v>
+        <f t="shared" si="50"/>
+        <v>220.56073418431799</v>
       </c>
       <c r="CW39" s="2">
-        <f t="shared" si="45"/>
-        <v>186.38773609690654</v>
+        <f t="shared" si="50"/>
+        <v>218.35512684247482</v>
       </c>
       <c r="CX39" s="2">
-        <f t="shared" si="45"/>
-        <v>184.52385873593747</v>
+        <f t="shared" ref="CX39:EK39" si="51">CW39*(1+$AM$45)</f>
+        <v>216.17157557405008</v>
       </c>
       <c r="CY39" s="2">
-        <f t="shared" si="45"/>
-        <v>182.67862014857809</v>
+        <f t="shared" si="51"/>
+        <v>214.00985981830956</v>
       </c>
       <c r="CZ39" s="2">
-        <f t="shared" si="45"/>
-        <v>180.8518339470923</v>
+        <f t="shared" si="51"/>
+        <v>211.86976122012646</v>
       </c>
       <c r="DA39" s="2">
-        <f t="shared" si="45"/>
-        <v>179.04331560762137</v>
+        <f t="shared" si="51"/>
+        <v>209.7510636079252</v>
       </c>
       <c r="DB39" s="2">
-        <f t="shared" si="45"/>
-        <v>177.25288245154516</v>
+        <f t="shared" si="51"/>
+        <v>207.65355297184595</v>
       </c>
       <c r="DC39" s="2">
-        <f t="shared" si="45"/>
-        <v>175.4803536270297</v>
+        <f t="shared" si="51"/>
+        <v>205.5770174421275</v>
       </c>
       <c r="DD39" s="2">
-        <f t="shared" si="45"/>
-        <v>173.72555009075941</v>
+        <f t="shared" si="51"/>
+        <v>203.52124726770623</v>
       </c>
       <c r="DE39" s="2">
-        <f t="shared" si="45"/>
-        <v>171.98829458985182</v>
+        <f t="shared" si="51"/>
+        <v>201.48603479502916</v>
       </c>
       <c r="DF39" s="2">
-        <f t="shared" si="45"/>
-        <v>170.2684116439533</v>
+        <f t="shared" si="51"/>
+        <v>199.47117444707885</v>
       </c>
       <c r="DG39" s="2">
-        <f t="shared" si="45"/>
-        <v>168.56572752751376</v>
+        <f t="shared" si="51"/>
+        <v>197.47646270260807</v>
       </c>
       <c r="DH39" s="2">
-        <f t="shared" si="45"/>
-        <v>166.88007025223862</v>
+        <f t="shared" si="51"/>
+        <v>195.501698075582</v>
       </c>
       <c r="DI39" s="2">
-        <f t="shared" si="45"/>
-        <v>165.21126954971623</v>
+        <f t="shared" si="51"/>
+        <v>193.54668109482617</v>
       </c>
       <c r="DJ39" s="2">
-        <f t="shared" si="45"/>
-        <v>163.55915685421908</v>
+        <f t="shared" si="51"/>
+        <v>191.6112142838779</v>
       </c>
       <c r="DK39" s="2">
-        <f t="shared" si="45"/>
-        <v>161.92356528567689</v>
+        <f t="shared" si="51"/>
+        <v>189.69510214103911</v>
       </c>
       <c r="DL39" s="2">
-        <f t="shared" si="45"/>
-        <v>160.30432963282013</v>
+        <f t="shared" si="51"/>
+        <v>187.79815111962873</v>
       </c>
       <c r="DM39" s="2">
-        <f t="shared" si="45"/>
-        <v>158.70128633649193</v>
+        <f t="shared" si="51"/>
+        <v>185.92016960843245</v>
       </c>
       <c r="DN39" s="2">
-        <f t="shared" si="45"/>
-        <v>157.11427347312701</v>
+        <f t="shared" si="51"/>
+        <v>184.06096791234813</v>
       </c>
       <c r="DO39" s="2">
-        <f t="shared" si="45"/>
-        <v>155.54313073839575</v>
+        <f t="shared" si="51"/>
+        <v>182.22035823322466</v>
       </c>
       <c r="DP39" s="2">
-        <f t="shared" si="45"/>
-        <v>153.98769943101178</v>
+        <f t="shared" si="51"/>
+        <v>180.39815465089242</v>
       </c>
       <c r="DQ39" s="2">
-        <f t="shared" si="45"/>
-        <v>152.44782243670167</v>
+        <f t="shared" si="51"/>
+        <v>178.59417310438349</v>
       </c>
       <c r="DR39" s="2">
-        <f t="shared" si="45"/>
-        <v>150.92334421233465</v>
+        <f t="shared" si="51"/>
+        <v>176.80823137333965</v>
       </c>
       <c r="DS39" s="2">
-        <f t="shared" si="45"/>
-        <v>149.41411077021129</v>
+        <f t="shared" si="51"/>
+        <v>175.04014905960625</v>
       </c>
       <c r="DT39" s="2">
-        <f t="shared" si="45"/>
-        <v>147.91996966250917</v>
+        <f t="shared" si="51"/>
+        <v>173.28974756901019</v>
       </c>
       <c r="DU39" s="2">
-        <f t="shared" si="45"/>
-        <v>146.44076996588407</v>
+        <f t="shared" si="51"/>
+        <v>171.55685009332009</v>
       </c>
       <c r="DV39" s="2">
-        <f t="shared" si="45"/>
-        <v>144.97636226622524</v>
+        <f t="shared" si="51"/>
+        <v>169.84128159238688</v>
       </c>
       <c r="DW39" s="2">
-        <f t="shared" si="45"/>
-        <v>143.52659864356298</v>
+        <f t="shared" si="51"/>
+        <v>168.14286877646302</v>
       </c>
       <c r="DX39" s="2">
-        <f t="shared" si="45"/>
-        <v>142.09133265712734</v>
+        <f t="shared" si="51"/>
+        <v>166.4614400886984</v>
       </c>
       <c r="DY39" s="2">
-        <f t="shared" si="45"/>
-        <v>140.67041933055606</v>
+        <f t="shared" si="51"/>
+        <v>164.79682568781141</v>
       </c>
       <c r="DZ39" s="2">
-        <f t="shared" si="45"/>
-        <v>139.2637151372505</v>
+        <f t="shared" si="51"/>
+        <v>163.1488574309333</v>
       </c>
       <c r="EA39" s="2">
-        <f t="shared" si="45"/>
-        <v>137.871077985878</v>
+        <f t="shared" si="51"/>
+        <v>161.51736885662396</v>
       </c>
       <c r="EB39" s="2">
-        <f t="shared" si="45"/>
-        <v>136.49236720601922</v>
+        <f t="shared" si="51"/>
+        <v>159.90219516805772</v>
       </c>
       <c r="EC39" s="2">
-        <f t="shared" si="45"/>
-        <v>135.12744353395902</v>
+        <f t="shared" si="51"/>
+        <v>158.30317321637713</v>
       </c>
       <c r="ED39" s="2">
-        <f t="shared" si="45"/>
-        <v>133.77616909861942</v>
+        <f t="shared" si="51"/>
+        <v>156.72014148421337</v>
       </c>
       <c r="EE39" s="2">
-        <f t="shared" si="45"/>
-        <v>132.43840740763324</v>
+        <f t="shared" si="51"/>
+        <v>155.15294006937123</v>
       </c>
       <c r="EF39" s="2">
-        <f t="shared" si="45"/>
-        <v>131.1140233335569</v>
+        <f t="shared" si="51"/>
+        <v>153.60141066867752</v>
       </c>
       <c r="EG39" s="2">
-        <f t="shared" si="45"/>
-        <v>129.80288310022132</v>
-      </c>
-    </row>
-    <row r="40" spans="2:137">
+        <f t="shared" si="51"/>
+        <v>152.06539656199075</v>
+      </c>
+      <c r="EH39" s="2">
+        <f t="shared" si="51"/>
+        <v>150.54474259637084</v>
+      </c>
+      <c r="EI39" s="2">
+        <f t="shared" si="51"/>
+        <v>149.03929517040712</v>
+      </c>
+      <c r="EJ39" s="2">
+        <f t="shared" si="51"/>
+        <v>147.54890221870303</v>
+      </c>
+      <c r="EK39" s="2">
+        <f t="shared" si="51"/>
+        <v>146.07341319651601</v>
+      </c>
+    </row>
+    <row r="40" spans="2:141">
       <c r="B40" s="1" t="s">
         <v>2</v>
       </c>
@@ -4218,27 +4513,27 @@
         <v>168.8</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" ref="G40:L40" si="46">168.8</f>
+        <f t="shared" ref="G40:L40" si="52">168.8</f>
         <v>168.8</v>
       </c>
       <c r="H40" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>168.8</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>168.8</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>168.8</v>
       </c>
       <c r="K40" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>168.8</v>
       </c>
       <c r="L40" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>168.8</v>
       </c>
       <c r="M40" s="6">
@@ -4246,79 +4541,83 @@
         <v>168.8</v>
       </c>
       <c r="N40" s="6">
-        <f>168.8</f>
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="T40" s="6">
+        <f t="shared" ref="T40:Y40" si="53">168.8</f>
         <v>168.8</v>
       </c>
-      <c r="P40" s="6">
-        <f t="shared" ref="P40:W40" si="47">168.8</f>
+      <c r="U40" s="6">
+        <f t="shared" si="53"/>
         <v>168.8</v>
       </c>
-      <c r="Q40" s="6">
-        <f t="shared" si="47"/>
+      <c r="V40" s="6">
+        <f t="shared" si="53"/>
         <v>168.8</v>
       </c>
-      <c r="R40" s="6">
-        <f t="shared" si="47"/>
+      <c r="W40" s="6">
+        <f t="shared" si="53"/>
         <v>168.8</v>
       </c>
-      <c r="S40" s="6">
-        <f t="shared" si="47"/>
+      <c r="X40" s="6">
+        <f t="shared" si="53"/>
         <v>168.8</v>
       </c>
-      <c r="T40" s="6">
-        <f t="shared" si="47"/>
+      <c r="Y40" s="6">
+        <f t="shared" si="53"/>
         <v>168.8</v>
       </c>
-      <c r="U40" s="6">
-        <f t="shared" si="47"/>
-        <v>168.8</v>
-      </c>
-      <c r="V40" s="6">
-        <f t="shared" si="47"/>
-        <v>168.8</v>
-      </c>
-      <c r="W40" s="6">
-        <f t="shared" si="47"/>
-        <v>168.8</v>
-      </c>
-      <c r="X40" s="6">
-        <f t="shared" ref="X40:AF40" si="48">168.8</f>
-        <v>168.8</v>
-      </c>
-      <c r="Y40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
-      </c>
       <c r="Z40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AA40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AB40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AC40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AD40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AE40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
+        <f>170.3</f>
+        <v>170.3</v>
       </c>
       <c r="AF40" s="6">
-        <f t="shared" si="48"/>
-        <v>168.8</v>
-      </c>
-    </row>
-    <row r="41" spans="2:137">
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+      <c r="AG40" s="6">
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+      <c r="AH40" s="6">
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+      <c r="AI40" s="6">
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+      <c r="AJ40" s="6">
+        <f>170.3</f>
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:141">
       <c r="B41" s="1" t="s">
         <v>27</v>
       </c>
@@ -4327,107 +4626,111 @@
         <v>1.7772511848341419E-2</v>
       </c>
       <c r="G41" s="8">
-        <f t="shared" ref="G41:L41" si="49">G39/G40</f>
+        <f t="shared" ref="G41:L41" si="54">G39/G40</f>
         <v>7.7014218009478662E-3</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>4.6800947867298659E-2</v>
       </c>
       <c r="I41" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>1.8957345971563892E-2</v>
       </c>
       <c r="J41" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>2.3104265402842928E-2</v>
       </c>
       <c r="K41" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>2.6658767772511978E-2</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>1.7180094786729959E-2</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" ref="M41:N41" si="50">M39/M40</f>
+        <f t="shared" ref="M41:N41" si="55">M39/M40</f>
         <v>5.2725118483412457E-2</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" si="50"/>
-        <v>4.0962369668246401E-2</v>
-      </c>
-      <c r="P41" s="8">
-        <f t="shared" ref="P41:W41" si="51">P39/P40</f>
+        <f t="shared" si="55"/>
+        <v>3.3470346447445024E-2</v>
+      </c>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="T41" s="8">
+        <f t="shared" ref="T41:AA41" si="56">T39/T40</f>
         <v>6.4573459715639631E-2</v>
       </c>
-      <c r="Q41" s="8">
-        <f t="shared" si="51"/>
+      <c r="U41" s="8">
+        <f t="shared" si="56"/>
         <v>0.475710900473934</v>
       </c>
-      <c r="R41" s="8">
-        <f t="shared" si="51"/>
+      <c r="V41" s="8">
+        <f t="shared" si="56"/>
         <v>2.9620853080570848E-3</v>
       </c>
-      <c r="S41" s="8">
-        <f t="shared" si="51"/>
+      <c r="W41" s="8">
+        <f t="shared" si="56"/>
         <v>-0.19668246445497634</v>
       </c>
-      <c r="T41" s="8">
-        <f t="shared" si="51"/>
+      <c r="X41" s="8">
+        <f t="shared" si="56"/>
         <v>1.4218009478672283E-2</v>
       </c>
-      <c r="U41" s="8">
-        <f t="shared" si="51"/>
+      <c r="Y41" s="8">
+        <f t="shared" si="56"/>
         <v>9.6563981042653693E-2</v>
       </c>
-      <c r="V41" s="8">
-        <f t="shared" si="51"/>
-        <v>0.13752635071089997</v>
-      </c>
-      <c r="W41" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46769715639810433</v>
-      </c>
-      <c r="X41" s="8">
-        <f t="shared" ref="X41:AF41" si="52">X39/X40</f>
-        <v>0.84001299857819844</v>
-      </c>
-      <c r="Y41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.0983145989289091</v>
-      </c>
       <c r="Z41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.278732460804739</v>
+        <f t="shared" si="56"/>
+        <v>0.12918379330593016</v>
       </c>
       <c r="AA41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.4490967550376306</v>
+        <f t="shared" si="56"/>
+        <v>0.38592601291837825</v>
       </c>
       <c r="AB41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.6111924285482044</v>
+        <f t="shared" ref="AB41:AJ41" si="57">AB39/AB40</f>
+        <v>0.8462448854961836</v>
       </c>
       <c r="AC41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.7489799159674453</v>
+        <f t="shared" si="57"/>
+        <v>1.1957584751614796</v>
       </c>
       <c r="AD41" s="8">
-        <f t="shared" si="52"/>
-        <v>1.8943015894420514</v>
+        <f t="shared" si="57"/>
+        <v>1.4610152989453919</v>
       </c>
       <c r="AE41" s="8">
-        <f t="shared" si="52"/>
-        <v>2.0475421226967021</v>
+        <f t="shared" si="57"/>
+        <v>1.6435652439161952</v>
       </c>
       <c r="AF41" s="8">
-        <f t="shared" si="52"/>
-        <v>2.2091055350819788</v>
-      </c>
-    </row>
-    <row r="43" spans="2:137">
+        <f t="shared" si="57"/>
+        <v>1.8163489866368827</v>
+      </c>
+      <c r="AG41" s="8">
+        <f t="shared" si="57"/>
+        <v>1.9656947154251612</v>
+      </c>
+      <c r="AH41" s="8">
+        <f t="shared" si="57"/>
+        <v>2.1231585538213027</v>
+      </c>
+      <c r="AI41" s="8">
+        <f t="shared" si="57"/>
+        <v>2.2891540939684214</v>
+      </c>
+      <c r="AJ41" s="8">
+        <f t="shared" si="57"/>
+        <v>2.4641157040807511</v>
+      </c>
+    </row>
+    <row r="43" spans="2:141">
       <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
@@ -4436,12 +4739,12 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:K45" si="53">I22/E22-1</f>
+        <f t="shared" ref="I43:K45" si="58">I22/E22-1</f>
         <v>-2.4413145539906034E-2</v>
       </c>
       <c r="J43" s="10"/>
       <c r="K43" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>-3.8497652582159536E-2</v>
       </c>
       <c r="L43" s="10">
@@ -4449,80 +4752,96 @@
         <v>0.26666666666666683</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" ref="M43:N45" si="54">M22/I22-1</f>
+        <f t="shared" ref="M43:N45" si="59">M22/I22-1</f>
         <v>0.12993262752646784</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" si="54"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="P43" s="10"/>
+        <f t="shared" si="59"/>
+        <v>7.3239436619718434E-2</v>
+      </c>
+      <c r="O43" s="10">
+        <f t="shared" ref="O43:O45" si="60">O22/K22-1</f>
+        <v>-1</v>
+      </c>
+      <c r="P43" s="10">
+        <f t="shared" ref="P43:P45" si="61">P22/L22-1</f>
+        <v>-1</v>
+      </c>
       <c r="Q43" s="10">
-        <f t="shared" ref="Q43:T43" si="55">Q22/P22-1</f>
+        <f t="shared" ref="Q43:Q45" si="62">Q22/M22-1</f>
+        <v>-1</v>
+      </c>
+      <c r="R43" s="10">
+        <f t="shared" ref="R43:R45" si="63">R22/N22-1</f>
+        <v>-1</v>
+      </c>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10">
+        <f t="shared" ref="U43:X43" si="64">U22/T22-1</f>
         <v>-8.7674247982391873E-2</v>
       </c>
-      <c r="R43" s="10">
-        <f t="shared" si="55"/>
+      <c r="V43" s="10">
+        <f t="shared" si="64"/>
         <v>-0.11781262565339756</v>
       </c>
-      <c r="S43" s="10">
-        <f t="shared" si="55"/>
+      <c r="W43" s="10">
+        <f t="shared" si="64"/>
         <v>0.48222424794895158</v>
       </c>
-      <c r="T43" s="10">
-        <f t="shared" si="55"/>
+      <c r="X43" s="10">
+        <f t="shared" si="64"/>
         <v>0.23800738007380096</v>
       </c>
-      <c r="U43" s="10">
-        <f>U22/T22-1</f>
+      <c r="Y43" s="10">
+        <f>Y22/X22-1</f>
         <v>5.1664182811723691E-2</v>
       </c>
-      <c r="V43" s="10">
-        <f t="shared" ref="V43:AF43" si="56">V22/U22-1</f>
-        <v>0.11946150212564977</v>
-      </c>
-      <c r="W43" s="10">
-        <f t="shared" si="56"/>
+      <c r="Z43" s="10">
+        <f t="shared" ref="Z43:AJ43" si="65">Z22/Y22-1</f>
+        <v>0.10769957487009929</v>
+      </c>
+      <c r="AA43" s="10">
+        <f t="shared" si="65"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="X43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AB43" s="10">
+        <f t="shared" si="65"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="Y43" s="10">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="Z43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AC43" s="10">
+        <f t="shared" si="65"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AD43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AA43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AE43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AF43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AG43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AH43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AI43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF43" s="10">
-        <f t="shared" si="56"/>
+      <c r="AJ43" s="10">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:137">
+    <row r="44" spans="2:141">
       <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
@@ -4531,93 +4850,109 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>2.3200475907198204E-2</v>
       </c>
       <c r="J44" s="10"/>
       <c r="K44" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.17281780902167543</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" ref="L44:L45" si="57">L23/H23-1</f>
+        <f t="shared" ref="L44:L45" si="66">L23/H23-1</f>
         <v>0.11880165289256195</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.33837209302325566</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" si="54"/>
-        <v>0.16999999999999993</v>
-      </c>
-      <c r="P44" s="10"/>
+        <f t="shared" si="59"/>
+        <v>0.30690826727066778</v>
+      </c>
+      <c r="O44" s="10">
+        <f t="shared" si="60"/>
+        <v>-1</v>
+      </c>
+      <c r="P44" s="10">
+        <f t="shared" si="61"/>
+        <v>-1</v>
+      </c>
       <c r="Q44" s="10">
-        <f t="shared" ref="Q44:T44" si="58">Q23/P23-1</f>
+        <f t="shared" si="62"/>
+        <v>-1</v>
+      </c>
+      <c r="R44" s="10">
+        <f t="shared" si="63"/>
+        <v>-1</v>
+      </c>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10">
+        <f t="shared" ref="U44:X44" si="67">U23/T23-1</f>
         <v>0.12160035963137794</v>
       </c>
-      <c r="R44" s="10">
-        <f t="shared" si="58"/>
+      <c r="V44" s="10">
+        <f t="shared" si="67"/>
         <v>0.18657314629258526</v>
       </c>
-      <c r="S44" s="10">
-        <f t="shared" si="58"/>
+      <c r="W44" s="10">
+        <f t="shared" si="67"/>
         <v>-3.2089174125992215E-2</v>
       </c>
-      <c r="T44" s="10">
-        <f t="shared" si="58"/>
+      <c r="X44" s="10">
+        <f t="shared" si="67"/>
         <v>0.10713662537079038</v>
       </c>
-      <c r="U44" s="10">
-        <f>U23/T23-1</f>
+      <c r="Y44" s="10">
+        <f>Y23/X23-1</f>
         <v>0.12356185973207245</v>
       </c>
-      <c r="V44" s="10">
-        <f t="shared" ref="V44:AF44" si="59">V23/U23-1</f>
-        <v>0.19739374386309438</v>
-      </c>
-      <c r="W44" s="10">
-        <f t="shared" si="59"/>
+      <c r="Z44" s="10">
+        <f t="shared" ref="Z44:AJ44" si="68">Z23/Y23-1</f>
+        <v>0.23130873895356996</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="68"/>
         <v>0.25</v>
       </c>
-      <c r="X44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AB44" s="10">
+        <f t="shared" si="68"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="Y44" s="10">
-        <f t="shared" si="59"/>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="Z44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AC44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AD44" s="10">
+        <f t="shared" si="68"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AA44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AE44" s="10">
+        <f t="shared" si="68"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AB44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AF44" s="10">
+        <f t="shared" si="68"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AG44" s="10">
+        <f t="shared" si="68"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AH44" s="10">
+        <f t="shared" si="68"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AI44" s="10">
+        <f t="shared" si="68"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF44" s="10">
-        <f t="shared" si="59"/>
+      <c r="AJ44" s="10">
+        <f t="shared" si="68"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:137">
+    <row r="45" spans="2:141">
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
@@ -4626,125 +4961,141 @@
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>4.73415877640182E-3</v>
       </c>
       <c r="J45" s="10"/>
       <c r="K45" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>9.1630591630591729E-2</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="66"/>
         <v>0.17127624125291563</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.2598767669445452</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" si="54"/>
-        <v>0.15119039208760165</v>
-      </c>
-      <c r="P45" s="10"/>
+        <f t="shared" si="59"/>
+        <v>0.21900388555280803</v>
+      </c>
+      <c r="O45" s="10">
+        <f t="shared" si="60"/>
+        <v>0.12359550561797739</v>
+      </c>
+      <c r="P45" s="10">
+        <f t="shared" si="61"/>
+        <v>0.14999999999999991</v>
+      </c>
       <c r="Q45" s="10">
-        <f t="shared" ref="Q45:T45" si="60">Q24/P24-1</f>
+        <f t="shared" si="62"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="R45" s="10">
+        <f t="shared" si="63"/>
+        <v>0.25</v>
+      </c>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10">
+        <f t="shared" ref="U45:X45" si="69">U24/T24-1</f>
         <v>4.2090592334494747E-2</v>
       </c>
-      <c r="R45" s="10">
-        <f t="shared" si="60"/>
+      <c r="V45" s="10">
+        <f t="shared" si="69"/>
         <v>8.532834024341307E-2</v>
       </c>
-      <c r="S45" s="10">
-        <f t="shared" si="60"/>
+      <c r="W45" s="10">
+        <f t="shared" si="69"/>
         <v>0.106962415280345</v>
       </c>
-      <c r="T45" s="10">
-        <f t="shared" si="60"/>
+      <c r="X45" s="10">
+        <f t="shared" si="69"/>
         <v>0.15451408215518203</v>
       </c>
-      <c r="U45" s="10">
-        <f>U24/T24-1</f>
+      <c r="Y45" s="10">
+        <f>Y24/X24-1</f>
         <v>9.5651335454633113E-2</v>
       </c>
-      <c r="V45" s="10">
-        <f t="shared" ref="V45:AF45" si="61">V24/U24-1</f>
-        <v>0.16835518789052206</v>
-      </c>
-      <c r="W45" s="10">
-        <f t="shared" si="61"/>
-        <v>0.19644705265584106</v>
-      </c>
-      <c r="X45" s="10">
-        <f t="shared" si="61"/>
-        <v>0.17732881811351064</v>
-      </c>
-      <c r="Y45" s="10">
-        <f t="shared" si="61"/>
-        <v>0.11568859658436148</v>
-      </c>
       <c r="Z45" s="10">
-        <f t="shared" si="61"/>
-        <v>7.1338279438096563E-2</v>
+        <f t="shared" ref="Z45:AJ45" si="70">Z24/Y24-1</f>
+        <v>0.18525037402094524</v>
       </c>
       <c r="AA45" s="10">
-        <f t="shared" si="61"/>
-        <v>5.7170266147629434E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.18259578259578246</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
+        <v>0.19354060977447407</v>
+      </c>
+      <c r="AC45" s="10">
+        <f t="shared" si="70"/>
+        <v>0.12633506156837337</v>
+      </c>
+      <c r="AD45" s="10">
+        <f t="shared" si="70"/>
+        <v>7.156950993564215E-2</v>
+      </c>
+      <c r="AE45" s="10">
+        <f t="shared" si="70"/>
+        <v>5.724640212775145E-2</v>
+      </c>
+      <c r="AF45" s="10">
+        <f t="shared" si="70"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="AG45" s="10">
+        <f t="shared" si="70"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC45" s="10">
-        <f t="shared" si="61"/>
+      <c r="AH45" s="10">
+        <f t="shared" si="70"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD45" s="10">
-        <f t="shared" si="61"/>
+      <c r="AI45" s="10">
+        <f t="shared" si="70"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE45" s="10">
-        <f t="shared" si="61"/>
+      <c r="AJ45" s="10">
+        <f t="shared" si="70"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF45" s="10">
-        <f t="shared" si="61"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AH45" s="1" t="s">
+      <c r="AL45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AI45" s="10">
+      <c r="AM45" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="46" spans="2:137">
+    <row r="46" spans="2:141">
       <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" ref="E46" si="62">(E22-E25)/E25</f>
+        <f t="shared" ref="E46" si="71">(E22-E25)/E25</f>
         <v>0.34810126582278483</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="10">
-        <f t="shared" ref="G46:K46" si="63">(G22-G25)/G22</f>
+        <f t="shared" ref="G46:K46" si="72">(G22-G25)/G22</f>
         <v>0.25633802816901408</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="72"/>
         <v>0.27699530516431925</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="72"/>
         <v>0.26179018286814248</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="72"/>
         <v>0.27605633802816892</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="72"/>
         <v>0.2607421875</v>
       </c>
       <c r="L46" s="10">
@@ -4752,115 +5103,131 @@
         <v>0.20533728687916977</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" ref="M46:N46" si="64">(M22-M25)/M22</f>
+        <f t="shared" ref="M46:N46" si="73">(M22-M25)/M22</f>
         <v>0.22316865417376491</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="64"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="P46" s="10">
-        <f t="shared" ref="P46:U46" si="65">(P22-P25)/P22</f>
+        <f t="shared" si="73"/>
+        <v>0.27646544181977234</v>
+      </c>
+      <c r="O46" s="10" t="e">
+        <f t="shared" ref="O46:R46" si="74">(O22-O25)/O22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P46" s="10" t="e">
+        <f t="shared" si="74"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q46" s="10" t="e">
+        <f t="shared" si="74"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R46" s="10" t="e">
+        <f t="shared" si="74"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="10">
+        <f t="shared" ref="T46:Y46" si="75">(T22-T25)/T22</f>
         <v>0.2956713132795305</v>
       </c>
-      <c r="Q46" s="10">
-        <f t="shared" si="65"/>
+      <c r="U46" s="10">
+        <f t="shared" si="75"/>
         <v>0.266184157619622</v>
       </c>
-      <c r="R46" s="10">
-        <f t="shared" si="65"/>
+      <c r="V46" s="10">
+        <f t="shared" si="75"/>
         <v>0.28805834092980864</v>
       </c>
-      <c r="S46" s="10">
-        <f t="shared" si="65"/>
+      <c r="W46" s="10">
+        <f t="shared" si="75"/>
         <v>0.26506765067650673</v>
       </c>
-      <c r="T46" s="10">
-        <f t="shared" si="65"/>
+      <c r="X46" s="10">
+        <f t="shared" si="75"/>
         <v>0.24689518132141089</v>
       </c>
-      <c r="U46" s="10">
-        <f t="shared" si="65"/>
+      <c r="Y46" s="10">
+        <f t="shared" si="75"/>
         <v>0.26783183750590456</v>
       </c>
-      <c r="V46" s="10">
-        <f t="shared" ref="V46:AF46" si="66">(V22-V25)/V22</f>
-        <v>0.23296341617789779</v>
-      </c>
-      <c r="W46" s="10">
-        <f t="shared" si="66"/>
+      <c r="Z46" s="10">
+        <f t="shared" ref="Z46:AJ46" si="76">(Z22-Z25)/Z22</f>
+        <v>0.2392324093816631</v>
+      </c>
+      <c r="AA46" s="10">
+        <f t="shared" si="76"/>
         <v>0.25</v>
       </c>
-      <c r="X46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AB46" s="10">
+        <f t="shared" si="76"/>
         <v>0.26</v>
       </c>
-      <c r="Y46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AC46" s="10">
+        <f t="shared" si="76"/>
         <v>0.27000000000000007</v>
       </c>
-      <c r="Z46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AD46" s="10">
+        <f t="shared" si="76"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AA46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AE46" s="10">
+        <f t="shared" si="76"/>
         <v>0.29000000000000004</v>
       </c>
-      <c r="AB46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AF46" s="10">
+        <f t="shared" si="76"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AC46" s="10">
-        <f t="shared" si="66"/>
-        <v>0.3000000000000001</v>
-      </c>
-      <c r="AD46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AG46" s="10">
+        <f t="shared" si="76"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AE46" s="10">
-        <f t="shared" si="66"/>
+      <c r="AH46" s="10">
+        <f t="shared" si="76"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI46" s="10">
+        <f t="shared" si="76"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AF46" s="10">
-        <f t="shared" si="66"/>
-        <v>0.3</v>
-      </c>
-      <c r="AH46" s="1" t="s">
+      <c r="AJ46" s="10">
+        <f t="shared" si="76"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AL46" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AI46" s="10">
+      <c r="AM46" s="10">
         <v>0.09</v>
       </c>
     </row>
-    <row r="47" spans="2:137">
+    <row r="47" spans="2:141">
       <c r="B47" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E47" s="10">
-        <f t="shared" ref="E47" si="67">(E23-E26)/E26</f>
+        <f t="shared" ref="E47" si="77">(E23-E26)/E26</f>
         <v>0.3756137479541734</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="10">
-        <f t="shared" ref="G47:K47" si="68">(G23-G26)/G23</f>
+        <f t="shared" ref="G47:K47" si="78">(G23-G26)/G23</f>
         <v>0.25600468658465136</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0.2463842975206611</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0.2441860465116279</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0.22876557191392938</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0.23426573426573416</v>
       </c>
       <c r="L47" s="10">
@@ -4868,113 +5235,129 @@
         <v>0.21283471837488455</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" ref="M47:N47" si="69">(M23-M26)/M23</f>
+        <f t="shared" ref="M47:N47" si="79">(M23-M26)/M23</f>
         <v>0.22111207645525621</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="69"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="P47" s="10">
-        <f t="shared" ref="P47:U47" si="70">(P23-P26)/P23</f>
+        <f t="shared" si="79"/>
+        <v>0.22443674176776396</v>
+      </c>
+      <c r="O47" s="10" t="e">
+        <f t="shared" ref="O47:R47" si="80">(O23-O26)/O23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P47" s="10" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q47" s="10" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R47" s="10" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="10">
+        <f t="shared" ref="T47:Y47" si="81">(T23-T26)/T23</f>
         <v>0.24589795459653851</v>
       </c>
-      <c r="Q47" s="10">
-        <f t="shared" si="70"/>
+      <c r="U47" s="10">
+        <f t="shared" si="81"/>
         <v>0.27454909819639278</v>
       </c>
-      <c r="R47" s="10">
-        <f t="shared" si="70"/>
+      <c r="V47" s="10">
+        <f t="shared" si="81"/>
         <v>0.2734335416314812</v>
       </c>
-      <c r="S47" s="10">
-        <f t="shared" si="70"/>
+      <c r="W47" s="10">
+        <f t="shared" si="81"/>
         <v>0.24393648577909616</v>
       </c>
-      <c r="T47" s="10">
-        <f t="shared" si="70"/>
+      <c r="X47" s="10">
+        <f t="shared" si="81"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="U47" s="10">
-        <f t="shared" si="70"/>
+      <c r="Y47" s="10">
+        <f t="shared" si="81"/>
         <v>0.24379295833917794</v>
       </c>
-      <c r="V47" s="10">
-        <f t="shared" ref="V47:AF47" si="71">(V23-V26)/V23</f>
-        <v>0.22424803953037759</v>
-      </c>
-      <c r="W47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.24</v>
-      </c>
-      <c r="X47" s="10">
-        <f t="shared" si="71"/>
+      <c r="Z47" s="10">
+        <f t="shared" ref="Z47:AJ47" si="82">(Z23-Z26)/Z23</f>
+        <v>0.22294372294372289</v>
+      </c>
+      <c r="AA47" s="10">
+        <f t="shared" si="82"/>
+        <v>0.24000000000000002</v>
+      </c>
+      <c r="AB47" s="10">
+        <f t="shared" si="82"/>
         <v>0.25</v>
       </c>
-      <c r="Y47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="Z47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.24999999999999997</v>
-      </c>
-      <c r="AA47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="AB47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
-      </c>
       <c r="AC47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
+        <f t="shared" si="82"/>
+        <v>0.25999999999999995</v>
       </c>
       <c r="AD47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
+        <f t="shared" si="82"/>
+        <v>0.27</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.24999999999999994</v>
+        <f t="shared" si="82"/>
+        <v>0.27</v>
       </c>
       <c r="AF47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="AH47" s="1" t="s">
+        <f t="shared" si="82"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AG47" s="10">
+        <f t="shared" si="82"/>
+        <v>0.27</v>
+      </c>
+      <c r="AH47" s="10">
+        <f t="shared" si="82"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AI47" s="10">
+        <f t="shared" si="82"/>
+        <v>0.27</v>
+      </c>
+      <c r="AJ47" s="10">
+        <f t="shared" si="82"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AL47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AI47" s="6">
-        <f>NPV(AI46,V39:EG39)</f>
-        <v>2779.9766219686608</v>
-      </c>
-    </row>
-    <row r="48" spans="2:137">
+      <c r="AM47" s="6">
+        <f>NPV(AM46,AA39:EK39)</f>
+        <v>3357.6029334831451</v>
+      </c>
+    </row>
+    <row r="48" spans="2:141">
       <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="10">
-        <f t="shared" ref="G48:K48" si="72">G28/G24</f>
+        <f t="shared" ref="G48:K48" si="83">G28/G24</f>
         <v>0.25613275613275616</v>
       </c>
       <c r="H48" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="83"/>
         <v>0.25724758413862048</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="83"/>
         <v>0.25081551286698078</v>
       </c>
       <c r="J48" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="83"/>
         <v>0.24655598728364503</v>
       </c>
       <c r="K48" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="83"/>
         <v>0.24322538003965638</v>
       </c>
       <c r="L48" s="10">
@@ -4982,90 +5365,106 @@
         <v>0.20995732574679946</v>
       </c>
       <c r="M48" s="10">
-        <f t="shared" ref="M48:N48" si="73">M28/M24</f>
+        <f t="shared" ref="M48:N48" si="84">M28/M24</f>
         <v>0.22180667433831996</v>
       </c>
       <c r="N48" s="10">
-        <f t="shared" si="73"/>
-        <v>0.23731999189940539</v>
+        <f t="shared" si="84"/>
+        <v>0.24166908142567339</v>
+      </c>
+      <c r="O48" s="10">
+        <f t="shared" ref="O48:R48" si="85">O28/O24</f>
+        <v>0</v>
       </c>
       <c r="P48" s="10">
-        <f t="shared" ref="P48:U48" si="74">P28/P24</f>
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="10">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="R48" s="10">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="10">
+        <f t="shared" ref="T48:Y48" si="86">T28/T24</f>
         <v>0.26480836236933797</v>
       </c>
-      <c r="Q48" s="10">
-        <f t="shared" si="74"/>
+      <c r="U48" s="10">
+        <f t="shared" si="86"/>
         <v>0.2717667513708707</v>
       </c>
-      <c r="R48" s="10">
-        <f t="shared" si="74"/>
+      <c r="V48" s="10">
+        <f t="shared" si="86"/>
         <v>0.27738755391250774</v>
       </c>
-      <c r="S48" s="10">
-        <f t="shared" si="74"/>
+      <c r="W48" s="10">
+        <f t="shared" si="86"/>
         <v>0.2515863297339419</v>
       </c>
-      <c r="T48" s="10">
-        <f t="shared" si="74"/>
+      <c r="X48" s="10">
+        <f t="shared" si="86"/>
         <v>0.25899141837816986</v>
       </c>
-      <c r="U48" s="10">
-        <f t="shared" si="74"/>
+      <c r="Y48" s="10">
+        <f t="shared" si="86"/>
         <v>0.25275015400862444</v>
       </c>
-      <c r="V48" s="10">
-        <f t="shared" ref="V48:AF48" si="75">V28/V24</f>
-        <v>0.22735960024163862</v>
-      </c>
-      <c r="W48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.24328239860665302</v>
-      </c>
-      <c r="X48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.25303892542695472</v>
-      </c>
-      <c r="Y48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.25577448037460243</v>
-      </c>
       <c r="Z48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.25848920155711136</v>
+        <f t="shared" ref="Z48:AJ48" si="87">Z28/Z24</f>
+        <v>0.22861597861597852</v>
       </c>
       <c r="AA48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.2612421646356598</v>
+        <f t="shared" si="87"/>
+        <v>0.23349050680596703</v>
       </c>
       <c r="AB48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.26405270579457485</v>
+        <f t="shared" si="87"/>
+        <v>0.25295811730395334</v>
       </c>
       <c r="AC48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.26405270579457479</v>
+        <f t="shared" si="87"/>
+        <v>0.26281016335478596</v>
       </c>
       <c r="AD48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.26405270579457485</v>
+        <f t="shared" si="87"/>
+        <v>0.27275359787224873</v>
       </c>
       <c r="AE48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.26405270579457468</v>
+        <f t="shared" si="87"/>
+        <v>0.2754694492410516</v>
       </c>
       <c r="AF48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.26405270579457479</v>
-      </c>
-      <c r="AH48" s="1" t="s">
+        <f t="shared" si="87"/>
+        <v>0.27820417386157731</v>
+      </c>
+      <c r="AG48" s="10">
+        <f t="shared" si="87"/>
+        <v>0.27820417386157736</v>
+      </c>
+      <c r="AH48" s="10">
+        <f t="shared" si="87"/>
+        <v>0.27820417386157742</v>
+      </c>
+      <c r="AI48" s="10">
+        <f t="shared" si="87"/>
+        <v>0.27820417386157725</v>
+      </c>
+      <c r="AJ48" s="10">
+        <f t="shared" si="87"/>
+        <v>0.27820417386157736</v>
+      </c>
+      <c r="AL48" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AI48" s="6">
+      <c r="AM48" s="6">
         <f>Main!D8</f>
-        <v>565.9</v>
-      </c>
-    </row>
-    <row r="49" spans="2:35">
+        <v>565.6</v>
+      </c>
+    </row>
+    <row r="49" spans="2:39">
       <c r="B49" s="1" t="s">
         <v>48</v>
       </c>
@@ -5074,12 +5473,12 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10">
-        <f t="shared" ref="I49:K49" si="76">I29/E29-1</f>
+        <f t="shared" ref="I49:K49" si="88">I29/E29-1</f>
         <v>3.3398821218074692E-2</v>
       </c>
       <c r="J49" s="10"/>
       <c r="K49" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>4.7794117647058876E-2</v>
       </c>
       <c r="L49" s="10">
@@ -5087,87 +5486,103 @@
         <v>9.9082568807339344E-2</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" ref="M49:N49" si="77">M29/I29-1</f>
+        <f t="shared" ref="M49:N49" si="89">M29/I29-1</f>
         <v>0.13688212927756638</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="77"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="P49" s="10"/>
+        <f t="shared" si="89"/>
+        <v>0.20952380952380878</v>
+      </c>
+      <c r="O49" s="10">
+        <f t="shared" ref="O49" si="90">O29/K29-1</f>
+        <v>-1</v>
+      </c>
+      <c r="P49" s="10">
+        <f t="shared" ref="P49" si="91">P29/L29-1</f>
+        <v>-1</v>
+      </c>
       <c r="Q49" s="10">
-        <f t="shared" ref="Q49:T49" si="78">Q29/P29-1</f>
+        <f t="shared" ref="Q49" si="92">Q29/M29-1</f>
+        <v>-1</v>
+      </c>
+      <c r="R49" s="10">
+        <f t="shared" ref="R49" si="93">R29/N29-1</f>
+        <v>-1</v>
+      </c>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10">
+        <f t="shared" ref="U49:X49" si="94">U29/T29-1</f>
         <v>0.10474006116207946</v>
       </c>
-      <c r="R49" s="10">
-        <f t="shared" si="78"/>
+      <c r="V49" s="10">
+        <f t="shared" si="94"/>
         <v>0.10865051903114176</v>
       </c>
-      <c r="S49" s="10">
-        <f t="shared" si="78"/>
+      <c r="W49" s="10">
+        <f t="shared" si="94"/>
         <v>0.14107365792759063</v>
       </c>
-      <c r="T49" s="10">
-        <f t="shared" si="78"/>
+      <c r="X49" s="10">
+        <f t="shared" si="94"/>
         <v>8.2056892778993529E-2</v>
       </c>
-      <c r="U49" s="10">
-        <f>U29/T29-1</f>
+      <c r="Y49" s="10">
+        <f>Y29/X29-1</f>
         <v>8.1900910010111128E-2</v>
       </c>
-      <c r="V49" s="10">
-        <f t="shared" ref="V49:AF49" si="79">V29/U29-1</f>
-        <v>9.0654205607476612E-2</v>
-      </c>
-      <c r="W49" s="10">
-        <f t="shared" si="79"/>
+      <c r="Z49" s="10">
+        <f t="shared" ref="Z49:AJ49" si="95">Z29/Y29-1</f>
+        <v>0.12242990654205599</v>
+      </c>
+      <c r="AA49" s="10">
+        <f t="shared" si="95"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="X49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AB49" s="10">
+        <f t="shared" si="95"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Y49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AC49" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AD49" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AE49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AB49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AF49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AG49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AH49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AI49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF49" s="10">
-        <f t="shared" si="79"/>
+      <c r="AJ49" s="10">
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH49" s="1" t="s">
+      <c r="AL49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AI49" s="6">
-        <f>AI47+AI48</f>
-        <v>3345.8766219686609</v>
-      </c>
-    </row>
-    <row r="50" spans="2:35">
+      <c r="AM49" s="6">
+        <f>AM47+AM48</f>
+        <v>3923.202933483145</v>
+      </c>
+    </row>
+    <row r="50" spans="2:39">
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
@@ -5176,12 +5591,12 @@
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
       <c r="I50" s="10">
-        <f t="shared" ref="I50:K50" si="80">I31/E31-1</f>
+        <f t="shared" ref="I50:K50" si="96">I31/E31-1</f>
         <v>-3.8834951456310662E-2</v>
       </c>
       <c r="J50" s="10"/>
       <c r="K50" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>4.1666666666666741E-2</v>
       </c>
       <c r="L50" s="10">
@@ -5189,113 +5604,129 @@
         <v>0</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" ref="M50:N50" si="81">M31/I31-1</f>
+        <f t="shared" ref="M50:N50" si="97">M31/I31-1</f>
         <v>1.0101010101010166E-2</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="81"/>
-        <v>3.7735849056603765E-2</v>
-      </c>
-      <c r="P50" s="10"/>
+        <f t="shared" si="97"/>
+        <v>-7.5471698113207419E-2</v>
+      </c>
+      <c r="O50" s="10">
+        <f t="shared" ref="O50" si="98">O31/K31-1</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="P50" s="10">
+        <f t="shared" ref="P50" si="99">P31/L31-1</f>
+        <v>0.14705882352941169</v>
+      </c>
       <c r="Q50" s="10">
-        <f t="shared" ref="Q50:T50" si="82">Q31/P31-1</f>
+        <f t="shared" ref="Q50" si="100">Q31/M31-1</f>
+        <v>0.18000000000000016</v>
+      </c>
+      <c r="R50" s="10">
+        <f t="shared" ref="R50" si="101">R31/N31-1</f>
+        <v>0.22448979591836715</v>
+      </c>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10">
+        <f t="shared" ref="U50:X50" si="102">U31/T31-1</f>
         <v>0.5</v>
       </c>
-      <c r="R50" s="10">
-        <f t="shared" si="82"/>
+      <c r="V50" s="10">
+        <f t="shared" si="102"/>
         <v>0.30370370370370381</v>
       </c>
-      <c r="S50" s="10">
-        <f t="shared" si="82"/>
+      <c r="W50" s="10">
+        <f t="shared" si="102"/>
         <v>9.659090909090895E-2</v>
       </c>
-      <c r="T50" s="10">
-        <f t="shared" si="82"/>
+      <c r="X50" s="10">
+        <f t="shared" si="102"/>
         <v>-5.1813471502590858E-3</v>
       </c>
-      <c r="U50" s="10">
-        <f>U31/T31-1</f>
+      <c r="Y50" s="10">
+        <f>Y31/X31-1</f>
         <v>4.9479166666666741E-2</v>
       </c>
-      <c r="V50" s="10">
-        <f t="shared" ref="V50:AF50" si="83">V31/U31-1</f>
-        <v>2.2332506203474045E-2</v>
-      </c>
-      <c r="W50" s="10">
-        <f t="shared" si="83"/>
+      <c r="Z50" s="10">
+        <f t="shared" ref="Z50:AJ50" si="103">Z31/Y31-1</f>
+        <v>-7.4441687344912744E-3</v>
+      </c>
+      <c r="AA50" s="10">
+        <f t="shared" si="103"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AB50" s="10">
+        <f t="shared" si="103"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AC50" s="10">
+        <f t="shared" si="103"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AD50" s="10">
+        <f t="shared" si="103"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="X50" s="10">
-        <f t="shared" si="83"/>
+      <c r="AF50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y50" s="10">
-        <f t="shared" si="83"/>
+      <c r="AG50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z50" s="10">
-        <f t="shared" si="83"/>
+      <c r="AH50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA50" s="10">
-        <f t="shared" si="83"/>
+      <c r="AI50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB50" s="10">
-        <f t="shared" si="83"/>
+      <c r="AJ50" s="10">
+        <f t="shared" si="103"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC50" s="10">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD50" s="10">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AE50" s="10">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AF50" s="10">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH50" s="1" t="s">
+      <c r="AL50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AI50" s="4">
-        <f>AI49/AF40</f>
-        <v>19.821543969008655</v>
-      </c>
-    </row>
-    <row r="51" spans="2:35">
+      <c r="AM50" s="4">
+        <f>AM49/AJ40</f>
+        <v>23.037010766195799</v>
+      </c>
+    </row>
+    <row r="51" spans="2:39">
       <c r="B51" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" ref="E51:K51" si="84">E34/E24</f>
+        <f t="shared" ref="E51:K51" si="104">E34/E24</f>
         <v>4.4428259286234631E-2</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="104"/>
         <v>2.5252525252525252E-2</v>
       </c>
       <c r="H51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="104"/>
         <v>4.1652782405864758E-2</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="104"/>
         <v>2.3559260601667222E-2</v>
       </c>
       <c r="J51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="104"/>
         <v>1.0596962204167738E-2</v>
       </c>
       <c r="K51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="104"/>
         <v>2.1810971579643165E-2</v>
       </c>
       <c r="L51" s="10">
@@ -5303,116 +5734,132 @@
         <v>1.0526315789473733E-2</v>
       </c>
       <c r="M51" s="10">
-        <f t="shared" ref="M51:N51" si="85">M34/M24</f>
+        <f t="shared" ref="M51:N51" si="105">M34/M24</f>
         <v>2.0425776754890743E-2</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="85"/>
-        <v>2.9588833453001184E-2</v>
+        <f t="shared" si="105"/>
+        <v>2.3761228629382472E-2</v>
+      </c>
+      <c r="O51" s="10">
+        <f t="shared" ref="O51:R51" si="106">O34/O24</f>
+        <v>8.8235294117647058E-3</v>
       </c>
       <c r="P51" s="10">
-        <f t="shared" ref="P51:T51" si="86">P34/P24</f>
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="10">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="R51" s="10">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="10">
+        <f t="shared" ref="T51:X51" si="107">T34/T24</f>
         <v>5.2961672473867558E-2</v>
       </c>
-      <c r="Q51" s="10">
-        <f t="shared" si="86"/>
+      <c r="U51" s="10">
+        <f t="shared" si="107"/>
         <v>3.9186839641567564E-2</v>
       </c>
-      <c r="R51" s="10">
-        <f t="shared" si="86"/>
+      <c r="V51" s="10">
+        <f t="shared" si="107"/>
         <v>3.4380776340110948E-2</v>
       </c>
-      <c r="S51" s="10">
-        <f t="shared" si="86"/>
+      <c r="W51" s="10">
+        <f t="shared" si="107"/>
         <v>-3.2283201603028008E-3</v>
       </c>
-      <c r="T51" s="10">
-        <f t="shared" si="86"/>
+      <c r="X51" s="10">
+        <f t="shared" si="107"/>
         <v>2.9987465046764906E-2</v>
       </c>
-      <c r="U51" s="10">
-        <f>U34/U24</f>
+      <c r="Y51" s="10">
+        <f>Y34/Y24</f>
         <v>2.5521429200035153E-2</v>
       </c>
-      <c r="V51" s="10">
-        <f t="shared" ref="V51:AF51" si="87">V34/V24</f>
-        <v>2.0369854820947775E-2</v>
-      </c>
-      <c r="W51" s="10">
-        <f t="shared" si="87"/>
-        <v>6.4008277483300083E-2</v>
-      </c>
-      <c r="X51" s="10">
-        <f t="shared" si="87"/>
-        <v>9.6423564690489946E-2</v>
-      </c>
-      <c r="Y51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.11259145561280462</v>
-      </c>
       <c r="Z51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.1221674738077459</v>
+        <f t="shared" ref="Z51:AJ51" si="108">Z34/Z24</f>
+        <v>1.9008019008018941E-2</v>
       </c>
       <c r="AA51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.13081430311573944</v>
+        <f t="shared" si="108"/>
+        <v>4.7765457833140651E-2</v>
       </c>
       <c r="AB51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.13841019407022051</v>
+        <f t="shared" si="108"/>
+        <v>9.1471470444655839E-2</v>
       </c>
       <c r="AC51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.14301848284433513</v>
+        <f t="shared" si="108"/>
+        <v>0.11587307175716335</v>
       </c>
       <c r="AD51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.14745630612109997</v>
+        <f t="shared" si="108"/>
+        <v>0.13266052903395384</v>
       </c>
       <c r="AE51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.15173001244248874</v>
+        <f t="shared" si="108"/>
+        <v>0.14141538591448433</v>
       </c>
       <c r="AF51" s="10">
-        <f t="shared" si="87"/>
-        <v>0.15584571265502159</v>
-      </c>
-      <c r="AH51" s="1" t="s">
+        <f t="shared" si="108"/>
+        <v>0.14904176374760364</v>
+      </c>
+      <c r="AG51" s="10">
+        <f t="shared" si="108"/>
+        <v>0.15375321593059751</v>
+      </c>
+      <c r="AH51" s="10">
+        <f t="shared" si="108"/>
+        <v>0.15829115623757029</v>
+      </c>
+      <c r="AI51" s="10">
+        <f t="shared" si="108"/>
+        <v>0.16266202401570357</v>
+      </c>
+      <c r="AJ51" s="10">
+        <f t="shared" si="108"/>
+        <v>0.16687201817883121</v>
+      </c>
+      <c r="AL51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AI51" s="4">
+      <c r="AM51" s="4">
         <f>Main!D3</f>
-        <v>69.14</v>
-      </c>
-    </row>
-    <row r="52" spans="2:35">
+        <v>91.31</v>
+      </c>
+    </row>
+    <row r="52" spans="2:39">
       <c r="B52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="10">
-        <f t="shared" ref="E52:K52" si="88">E38/E37</f>
+        <f t="shared" ref="E52:K52" si="109">E38/E37</f>
         <v>0.55882352941176205</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="109"/>
         <v>0.67500000000000004</v>
       </c>
       <c r="H52" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="109"/>
         <v>0.37795275590551142</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="109"/>
         <v>0.44827586206896664</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="109"/>
         <v>2.5000000000000626E-2</v>
       </c>
       <c r="K52" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="109"/>
         <v>0.16666666666666596</v>
       </c>
       <c r="L52" s="10">
@@ -5420,116 +5867,132 @@
         <v>0.36956521739130294</v>
       </c>
       <c r="M52" s="10">
-        <f t="shared" ref="M52:N52" si="89">M38/M37</f>
+        <f t="shared" ref="M52:N52" si="110">M38/M37</f>
         <v>0.26446280991735488</v>
       </c>
       <c r="N52" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="110"/>
+        <v>0.52100840336134946</v>
+      </c>
+      <c r="O52" s="10" t="e">
+        <f t="shared" ref="O52:R52" si="111">O38/O37</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P52" s="10" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q52" s="10" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R52" s="10" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T52" s="10">
+        <f t="shared" ref="T52:X52" si="112">T38/T37</f>
+        <v>0.30573248407643366</v>
+      </c>
+      <c r="U52" s="10">
+        <f t="shared" si="112"/>
+        <v>-10.808823529411658</v>
+      </c>
+      <c r="V52" s="10">
+        <f t="shared" si="112"/>
+        <v>0.88636363636362914</v>
+      </c>
+      <c r="W52" s="10">
+        <f t="shared" si="112"/>
+        <v>-6.0606060606060597E-3</v>
+      </c>
+      <c r="X52" s="10">
+        <f t="shared" si="112"/>
+        <v>0.7837837837837921</v>
+      </c>
+      <c r="Y52" s="10">
+        <f>Y38/Y37</f>
+        <v>0.38490566037735929</v>
+      </c>
+      <c r="Z52" s="10">
+        <f t="shared" ref="Z52:AJ52" si="113">Z38/Z37</f>
+        <v>0.3529411764705892</v>
+      </c>
+      <c r="AA52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="P52" s="10">
-        <f t="shared" ref="P52:T52" si="90">P38/P37</f>
-        <v>0.30573248407643366</v>
-      </c>
-      <c r="Q52" s="10">
-        <f t="shared" si="90"/>
-        <v>-10.808823529411658</v>
-      </c>
-      <c r="R52" s="10">
-        <f t="shared" si="90"/>
-        <v>0.88636363636362914</v>
-      </c>
-      <c r="S52" s="10">
-        <f t="shared" si="90"/>
-        <v>-6.0606060606060597E-3</v>
-      </c>
-      <c r="T52" s="10">
-        <f t="shared" si="90"/>
-        <v>0.7837837837837921</v>
-      </c>
-      <c r="U52" s="10">
-        <f>U38/U37</f>
-        <v>0.38490566037735929</v>
-      </c>
-      <c r="V52" s="10">
-        <f t="shared" ref="V52:AF52" si="91">V38/V37</f>
-        <v>0.24488817964119447</v>
-      </c>
-      <c r="W52" s="10">
-        <f t="shared" si="91"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="X52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AB52" s="10">
+        <f t="shared" si="113"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AC52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="Y52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AD52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="Z52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AE52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="AA52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AF52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="AB52" s="10">
-        <f t="shared" si="91"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AC52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AG52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="AD52" s="10">
-        <f t="shared" si="91"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AE52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AH52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="AF52" s="10">
-        <f t="shared" si="91"/>
+      <c r="AI52" s="10">
+        <f t="shared" si="113"/>
         <v>0.2</v>
       </c>
-      <c r="AH52" s="2" t="s">
+      <c r="AJ52" s="10">
+        <f t="shared" si="113"/>
+        <v>0.2</v>
+      </c>
+      <c r="AL52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AI52" s="11">
-        <f>AI50/AI51-1</f>
-        <v>-0.71331293073461599</v>
-      </c>
-    </row>
-    <row r="53" spans="2:35">
+      <c r="AM52" s="11">
+        <f>AM50/AM51-1</f>
+        <v>-0.74770550031545513</v>
+      </c>
+    </row>
+    <row r="53" spans="2:39">
       <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E53" s="10">
-        <f t="shared" ref="E53:K53" si="92">E39/E24</f>
+        <f t="shared" ref="E53:K53" si="114">E39/E24</f>
         <v>1.092498179169713E-2</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="114"/>
         <v>4.6897546897546891E-3</v>
       </c>
       <c r="H53" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="114"/>
         <v>2.6324558480506542E-2</v>
       </c>
       <c r="I53" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="114"/>
         <v>1.1598405219282296E-2</v>
       </c>
       <c r="J53" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="114"/>
         <v>1.377605086541818E-2</v>
       </c>
       <c r="K53" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="114"/>
         <v>1.4871116986120363E-2</v>
       </c>
       <c r="L53" s="10">
@@ -5537,104 +6000,120 @@
         <v>8.25035561877672E-3</v>
       </c>
       <c r="M53" s="10">
-        <f t="shared" ref="M53:N53" si="93">M39/M24</f>
+        <f t="shared" ref="M53:N53" si="115">M39/M24</f>
         <v>2.5604142692750353E-2</v>
       </c>
       <c r="N53" s="10">
-        <f t="shared" si="93"/>
-        <v>2.1216341108676821E-2</v>
+        <f t="shared" si="115"/>
+        <v>1.6516951608229181E-2</v>
+      </c>
+      <c r="O53" s="10">
+        <f t="shared" ref="O53:R53" si="116">O39/O24</f>
+        <v>0</v>
       </c>
       <c r="P53" s="10">
-        <f t="shared" ref="P53:T53" si="94">P39/P24</f>
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="10">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="R53" s="10">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="10">
+        <f t="shared" ref="T53:X53" si="117">T39/T24</f>
         <v>1.519163763066198E-2</v>
       </c>
-      <c r="Q53" s="10">
-        <f t="shared" si="94"/>
+      <c r="U53" s="10">
+        <f t="shared" si="117"/>
         <v>0.10739601444429593</v>
       </c>
-      <c r="R53" s="10">
-        <f t="shared" si="94"/>
+      <c r="V53" s="10">
+        <f t="shared" si="117"/>
         <v>6.1614294516332225E-4</v>
       </c>
-      <c r="S53" s="10">
-        <f t="shared" si="94"/>
+      <c r="W53" s="10">
+        <f t="shared" si="117"/>
         <v>-3.6958699766225102E-2</v>
       </c>
-      <c r="T53" s="10">
-        <f t="shared" si="94"/>
+      <c r="X53" s="10">
+        <f t="shared" si="117"/>
         <v>2.3141452126119772E-3</v>
       </c>
-      <c r="U53" s="10">
-        <f>U39/U24</f>
+      <c r="Y53" s="10">
+        <f>Y39/Y24</f>
         <v>1.4344803308985254E-2</v>
       </c>
-      <c r="V53" s="10">
-        <f t="shared" ref="V53:AF53" si="95">V39/V24</f>
-        <v>1.7485999569147918E-2</v>
-      </c>
-      <c r="W53" s="10">
-        <f t="shared" si="95"/>
-        <v>4.9702220245397048E-2</v>
-      </c>
-      <c r="X53" s="10">
-        <f t="shared" si="95"/>
-        <v>7.5822708148633747E-2</v>
-      </c>
-      <c r="Y53" s="10">
-        <f t="shared" si="95"/>
-        <v>8.885810509461918E-2</v>
-      </c>
       <c r="Z53" s="10">
-        <f t="shared" si="95"/>
-        <v>9.6565803502100922E-2</v>
+        <f t="shared" ref="Z53:AJ53" si="118">Z39/Z24</f>
+        <v>1.6335016335016266E-2</v>
       </c>
       <c r="AA53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.10351329015427119</v>
+        <f t="shared" si="118"/>
+        <v>4.1264754633582694E-2</v>
       </c>
       <c r="AB53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.10961168201001455</v>
+        <f t="shared" si="118"/>
+        <v>7.5811322183972893E-2</v>
       </c>
       <c r="AC53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.11331957918637599</v>
+        <f t="shared" si="118"/>
+        <v>9.5107305621214361E-2</v>
       </c>
       <c r="AD53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.11689069889519914</v>
+        <f t="shared" si="118"/>
+        <v>0.10844382473769805</v>
       </c>
       <c r="AE53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.1203301276856755</v>
+        <f t="shared" si="118"/>
+        <v>0.11538803979962549</v>
       </c>
       <c r="AF53" s="10">
-        <f t="shared" si="95"/>
-        <v>0.1236427618036697</v>
-      </c>
-      <c r="AH53" s="1" t="s">
+        <f t="shared" si="118"/>
+        <v>0.12144617576006309</v>
+      </c>
+      <c r="AG53" s="10">
+        <f t="shared" si="118"/>
+        <v>0.12517318960622997</v>
+      </c>
+      <c r="AH53" s="10">
+        <f t="shared" si="118"/>
+        <v>0.12876219676872722</v>
+      </c>
+      <c r="AI53" s="10">
+        <f t="shared" si="118"/>
+        <v>0.13221833343354489</v>
+      </c>
+      <c r="AJ53" s="10">
+        <f t="shared" si="118"/>
+        <v>0.13554654373126637</v>
+      </c>
+      <c r="AL53" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AI53" s="7" t="s">
+      <c r="AM53" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="2:35">
+    <row r="56" spans="2:39">
       <c r="B56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:35">
+    <row r="57" spans="2:39">
       <c r="B57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="2:35">
+    <row r="58" spans="2:39">
       <c r="B58" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="2:35" s="34" customFormat="1">
+    <row r="60" spans="2:39" s="34" customFormat="1">
       <c r="B60" s="34" t="s">
         <v>100</v>
       </c>
@@ -5644,28 +6123,28 @@
       <c r="L60" s="34">
         <v>2585.6999999999998</v>
       </c>
-      <c r="V60" s="34">
+      <c r="Z60" s="34">
         <v>2423.3000000000002</v>
       </c>
     </row>
-    <row r="62" spans="2:35">
+    <row r="62" spans="2:39">
       <c r="B62" s="1" t="s">
         <v>101</v>
       </c>
       <c r="L62" s="35"/>
-      <c r="V62" s="35">
-        <f>Main!$D$9/Model!V60</f>
-        <v>4.5825659225023729</v>
-      </c>
-    </row>
-    <row r="63" spans="2:35">
+      <c r="Z62" s="35">
+        <f>Main!$D$9/Model!Z60</f>
+        <v>6.1835072009243595</v>
+      </c>
+    </row>
+    <row r="63" spans="2:39">
       <c r="B63" s="1" t="s">
         <v>102</v>
       </c>
       <c r="L63" s="10"/>
-      <c r="V63" s="10">
-        <f>V60/Main!$D$9-1</f>
-        <v>-0.78178164440808828</v>
+      <c r="Z63" s="10">
+        <f>Z60/Main!$D$9-1</f>
+        <v>-0.8382794799930835</v>
       </c>
     </row>
   </sheetData>
